--- a/research/traditional_assets/database/data/czech_republic/czech_republic_utility_general.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_utility_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0685888675710359</v>
+        <v>0.06849499872265093</v>
       </c>
       <c r="C2">
-        <v>111.8824079856003</v>
+        <v>111.0118750431616</v>
       </c>
       <c r="D2">
-        <v>89.78240798560026</v>
+        <v>90.03137504316163</v>
       </c>
       <c r="E2">
-        <v>-0.85</v>
+        <v>0.2695</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.1195</v>
       </c>
       <c r="G2">
         <v>22.1</v>
@@ -1451,28 +1451,28 @@
         <v>12.76</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05631085</v>
       </c>
       <c r="N2">
-        <v>12.76</v>
+        <v>12.70368915</v>
       </c>
       <c r="O2">
-        <v>2.4244</v>
+        <v>2.4137009385</v>
       </c>
       <c r="P2">
-        <v>10.3356</v>
+        <v>10.2899882115</v>
       </c>
       <c r="Q2">
-        <v>12.8756</v>
+        <v>12.8299882115</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0685888675710359</v>
+        <v>0.06877532194207164</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563937</v>
+        <v>0.4478317885952188</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>226.59931434173</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06849499872265093</v>
+        <v>0.06840112987426597</v>
       </c>
       <c r="C3">
-        <v>111.0118750431616</v>
+        <v>110.1427267140051</v>
       </c>
       <c r="D3">
-        <v>90.03137504316163</v>
+        <v>90.2817267140051</v>
       </c>
       <c r="E3">
-        <v>0.2695</v>
+        <v>1.389</v>
       </c>
       <c r="F3">
-        <v>1.1195</v>
+        <v>2.239</v>
       </c>
       <c r="G3">
         <v>22.1</v>
@@ -1533,28 +1533,28 @@
         <v>12.76</v>
       </c>
       <c r="M3">
-        <v>0.05631085</v>
+        <v>0.1126217</v>
       </c>
       <c r="N3">
-        <v>12.70368915</v>
+        <v>12.6473783</v>
       </c>
       <c r="O3">
-        <v>2.4137009385</v>
+        <v>2.403001877</v>
       </c>
       <c r="P3">
-        <v>10.2899882115</v>
+        <v>10.244376423</v>
       </c>
       <c r="Q3">
-        <v>12.8299882115</v>
+        <v>12.784376423</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06877532194207164</v>
+        <v>0.06896558150435303</v>
       </c>
       <c r="T3">
-        <v>0.4478317885952188</v>
+        <v>0.4515403015940199</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.59931434173</v>
+        <v>113.299657170865</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06840112987426597</v>
+        <v>0.068307261025881</v>
       </c>
       <c r="C4">
-        <v>110.1427267140051</v>
+        <v>109.2749745809876</v>
       </c>
       <c r="D4">
-        <v>90.2817267140051</v>
+        <v>90.53347458098759</v>
       </c>
       <c r="E4">
-        <v>1.389</v>
+        <v>2.508499999999999</v>
       </c>
       <c r="F4">
-        <v>2.239</v>
+        <v>3.358499999999999</v>
       </c>
       <c r="G4">
         <v>22.1</v>
@@ -1615,28 +1615,28 @@
         <v>12.76</v>
       </c>
       <c r="M4">
-        <v>0.1126217</v>
+        <v>0.16893255</v>
       </c>
       <c r="N4">
-        <v>12.6473783</v>
+        <v>12.59106745</v>
       </c>
       <c r="O4">
-        <v>2.403001877</v>
+        <v>2.3923028155</v>
       </c>
       <c r="P4">
-        <v>10.244376423</v>
+        <v>10.1987646345</v>
       </c>
       <c r="Q4">
-        <v>12.784376423</v>
+        <v>12.7387646345</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06896558150435303</v>
+        <v>0.06915976394420721</v>
       </c>
       <c r="T4">
-        <v>0.4515403015940199</v>
+        <v>0.4553252787783632</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.299657170865</v>
+        <v>75.53310478057666</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.068307261025881</v>
+        <v>0.06821339217749603</v>
       </c>
       <c r="C5">
-        <v>109.2749745809876</v>
+        <v>108.408630356521</v>
       </c>
       <c r="D5">
-        <v>90.53347458098759</v>
+        <v>90.78663035652104</v>
       </c>
       <c r="E5">
-        <v>2.508499999999999</v>
+        <v>3.628</v>
       </c>
       <c r="F5">
-        <v>3.358499999999999</v>
+        <v>4.478</v>
       </c>
       <c r="G5">
         <v>22.1</v>
@@ -1697,28 +1697,28 @@
         <v>12.76</v>
       </c>
       <c r="M5">
-        <v>0.16893255</v>
+        <v>0.2252434</v>
       </c>
       <c r="N5">
-        <v>12.59106745</v>
+        <v>12.5347566</v>
       </c>
       <c r="O5">
-        <v>2.3923028155</v>
+        <v>2.381603754</v>
       </c>
       <c r="P5">
-        <v>10.1987646345</v>
+        <v>10.153152846</v>
       </c>
       <c r="Q5">
-        <v>12.7387646345</v>
+        <v>12.693152846</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06915976394420721</v>
+        <v>0.06935799185155836</v>
       </c>
       <c r="T5">
-        <v>0.4553252787783632</v>
+        <v>0.459189109654047</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.53310478057666</v>
+        <v>56.64982858543248</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06821339217749603</v>
+        <v>0.06811952332911105</v>
       </c>
       <c r="C6">
-        <v>108.408630356521</v>
+        <v>107.5437058843889</v>
       </c>
       <c r="D6">
-        <v>90.78663035652104</v>
+        <v>91.04120588438889</v>
       </c>
       <c r="E6">
-        <v>3.628</v>
+        <v>4.7475</v>
       </c>
       <c r="F6">
-        <v>4.478</v>
+        <v>5.5975</v>
       </c>
       <c r="G6">
         <v>22.1</v>
@@ -1779,28 +1779,28 @@
         <v>12.76</v>
       </c>
       <c r="M6">
-        <v>0.2252434</v>
+        <v>0.28155425</v>
       </c>
       <c r="N6">
-        <v>12.5347566</v>
+        <v>12.47844575</v>
       </c>
       <c r="O6">
-        <v>2.381603754</v>
+        <v>2.3709046925</v>
       </c>
       <c r="P6">
-        <v>10.153152846</v>
+        <v>10.1075410575</v>
       </c>
       <c r="Q6">
-        <v>12.693152846</v>
+        <v>12.6475410575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06935799185155836</v>
+        <v>0.06956039297801163</v>
       </c>
       <c r="T6">
-        <v>0.459189109654047</v>
+        <v>0.4631342843376399</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.64982858543248</v>
+        <v>45.31986286834599</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06811952332911105</v>
+        <v>0.06802565448072609</v>
       </c>
       <c r="C7">
-        <v>107.5437058843889</v>
+        <v>106.680213141593</v>
       </c>
       <c r="D7">
-        <v>91.04120588438889</v>
+        <v>91.29721314159302</v>
       </c>
       <c r="E7">
-        <v>4.7475</v>
+        <v>5.867</v>
       </c>
       <c r="F7">
-        <v>5.5975</v>
+        <v>6.717</v>
       </c>
       <c r="G7">
         <v>22.1</v>
@@ -1861,28 +1861,28 @@
         <v>12.76</v>
       </c>
       <c r="M7">
-        <v>0.28155425</v>
+        <v>0.3378651</v>
       </c>
       <c r="N7">
-        <v>12.47844575</v>
+        <v>12.4221349</v>
       </c>
       <c r="O7">
-        <v>2.3709046925</v>
+        <v>2.360205631</v>
       </c>
       <c r="P7">
-        <v>10.1075410575</v>
+        <v>10.061929269</v>
       </c>
       <c r="Q7">
-        <v>12.6475410575</v>
+        <v>12.601929269</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06956039297801163</v>
+        <v>0.06976710051141073</v>
       </c>
       <c r="T7">
-        <v>0.4631342843376399</v>
+        <v>0.4671633989081179</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.31986286834599</v>
+        <v>37.76655239028832</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06802565448072609</v>
+        <v>0.06793178563234112</v>
       </c>
       <c r="C8">
-        <v>106.680213141593</v>
+        <v>105.8181642402324</v>
       </c>
       <c r="D8">
-        <v>91.29721314159302</v>
+        <v>91.5546642402324</v>
       </c>
       <c r="E8">
-        <v>5.866999999999999</v>
+        <v>6.986499999999999</v>
       </c>
       <c r="F8">
-        <v>6.716999999999999</v>
+        <v>7.836499999999998</v>
       </c>
       <c r="G8">
         <v>22.1</v>
@@ -1943,28 +1943,28 @@
         <v>12.76</v>
       </c>
       <c r="M8">
-        <v>0.3378650999999999</v>
+        <v>0.3941759499999999</v>
       </c>
       <c r="N8">
-        <v>12.4221349</v>
+        <v>12.36582405</v>
       </c>
       <c r="O8">
-        <v>2.360205631</v>
+        <v>2.3495065695</v>
       </c>
       <c r="P8">
-        <v>10.061929269</v>
+        <v>10.0163174805</v>
       </c>
       <c r="Q8">
-        <v>12.601929269</v>
+        <v>12.5563174805</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06976710051141073</v>
+        <v>0.06997825336810873</v>
       </c>
       <c r="T8">
-        <v>0.4671633989081179</v>
+        <v>0.4712791611037674</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.76655239028833</v>
+        <v>32.37133062024714</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06793178563234112</v>
+        <v>0.06783791678395616</v>
       </c>
       <c r="C9">
-        <v>105.8181642402324</v>
+        <v>104.9575714294129</v>
       </c>
       <c r="D9">
-        <v>91.5546642402324</v>
+        <v>91.81357142941292</v>
       </c>
       <c r="E9">
-        <v>6.9865</v>
+        <v>8.106</v>
       </c>
       <c r="F9">
-        <v>7.8365</v>
+        <v>8.956</v>
       </c>
       <c r="G9">
         <v>22.1</v>
@@ -2025,28 +2025,28 @@
         <v>12.76</v>
       </c>
       <c r="M9">
-        <v>0.39417595</v>
+        <v>0.4504868</v>
       </c>
       <c r="N9">
-        <v>12.36582405</v>
+        <v>12.3095132</v>
       </c>
       <c r="O9">
-        <v>2.3495065695</v>
+        <v>2.338807508</v>
       </c>
       <c r="P9">
-        <v>10.0163174805</v>
+        <v>9.970705692000001</v>
       </c>
       <c r="Q9">
-        <v>12.5563174805</v>
+        <v>12.510705692</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06997825336810873</v>
+        <v>0.07019399650430017</v>
       </c>
       <c r="T9">
-        <v>0.4712791611037674</v>
+        <v>0.4754843963906267</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.37133062024714</v>
+        <v>28.32491429271624</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06783791678395616</v>
+        <v>0.06774404793557118</v>
       </c>
       <c r="C10">
-        <v>104.9575714294129</v>
+        <v>104.0984470971904</v>
       </c>
       <c r="D10">
-        <v>91.81357142941292</v>
+        <v>92.07394709719043</v>
       </c>
       <c r="E10">
-        <v>8.106</v>
+        <v>9.225499999999998</v>
       </c>
       <c r="F10">
-        <v>8.956</v>
+        <v>10.0755</v>
       </c>
       <c r="G10">
         <v>22.1</v>
@@ -2107,28 +2107,28 @@
         <v>12.76</v>
       </c>
       <c r="M10">
-        <v>0.4504868</v>
+        <v>0.5067976499999999</v>
       </c>
       <c r="N10">
-        <v>12.3095132</v>
+        <v>12.25320235</v>
       </c>
       <c r="O10">
-        <v>2.338807508</v>
+        <v>2.3281084465</v>
       </c>
       <c r="P10">
-        <v>9.970705692000001</v>
+        <v>9.925093903500002</v>
       </c>
       <c r="Q10">
-        <v>12.510705692</v>
+        <v>12.4650939035</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07019399650430017</v>
+        <v>0.07041448124788041</v>
       </c>
       <c r="T10">
-        <v>0.4754843963906267</v>
+        <v>0.4797820544310432</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.32491429271624</v>
+        <v>25.17770159352555</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06774404793557118</v>
+        <v>0.06765017908718622</v>
       </c>
       <c r="C11">
-        <v>104.0984470971904</v>
+        <v>103.2408037725462</v>
       </c>
       <c r="D11">
-        <v>92.07394709719043</v>
+        <v>92.33580377254617</v>
       </c>
       <c r="E11">
-        <v>9.225499999999998</v>
+        <v>10.345</v>
       </c>
       <c r="F11">
-        <v>10.0755</v>
+        <v>11.195</v>
       </c>
       <c r="G11">
         <v>22.1</v>
@@ -2189,28 +2189,28 @@
         <v>12.76</v>
       </c>
       <c r="M11">
-        <v>0.5067976499999999</v>
+        <v>0.5631084999999999</v>
       </c>
       <c r="N11">
-        <v>12.25320235</v>
+        <v>12.1968915</v>
       </c>
       <c r="O11">
-        <v>2.3281084465</v>
+        <v>2.317409385</v>
       </c>
       <c r="P11">
-        <v>9.925093903500002</v>
+        <v>9.879482115000002</v>
       </c>
       <c r="Q11">
-        <v>12.4650939035</v>
+        <v>12.419482115</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07041448124788041</v>
+        <v>0.07063986565242913</v>
       </c>
       <c r="T11">
-        <v>0.4797820544310432</v>
+        <v>0.4841752159834692</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.17770159352555</v>
+        <v>22.65993143417299</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06765017908718622</v>
+        <v>0.06755631023880124</v>
       </c>
       <c r="C12">
-        <v>103.2408037725462</v>
+        <v>102.384654127397</v>
       </c>
       <c r="D12">
-        <v>92.33580377254617</v>
+        <v>92.599154127397</v>
       </c>
       <c r="E12">
-        <v>10.345</v>
+        <v>11.4645</v>
       </c>
       <c r="F12">
-        <v>11.195</v>
+        <v>12.3145</v>
       </c>
       <c r="G12">
         <v>22.1</v>
@@ -2271,28 +2271,28 @@
         <v>12.76</v>
       </c>
       <c r="M12">
-        <v>0.5631085</v>
+        <v>0.6194193499999999</v>
       </c>
       <c r="N12">
-        <v>12.1968915</v>
+        <v>12.14058065</v>
       </c>
       <c r="O12">
-        <v>2.317409385</v>
+        <v>2.3067103235</v>
       </c>
       <c r="P12">
-        <v>9.879482115000002</v>
+        <v>9.833870326500001</v>
       </c>
       <c r="Q12">
-        <v>12.419482115</v>
+        <v>12.3738703265</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07063986565242913</v>
+        <v>0.07087031487505757</v>
       </c>
       <c r="T12">
-        <v>0.4841752159834692</v>
+        <v>0.4886671002674102</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.65993143417299</v>
+        <v>20.59993766742999</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06755631023880124</v>
+        <v>0.06746244139041628</v>
       </c>
       <c r="C13">
-        <v>102.384654127397</v>
+        <v>101.5300109786389</v>
       </c>
       <c r="D13">
-        <v>92.599154127397</v>
+        <v>92.86401097863892</v>
       </c>
       <c r="E13">
-        <v>11.4645</v>
+        <v>12.584</v>
       </c>
       <c r="F13">
-        <v>12.3145</v>
+        <v>13.434</v>
       </c>
       <c r="G13">
         <v>22.1</v>
@@ -2353,28 +2353,28 @@
         <v>12.76</v>
       </c>
       <c r="M13">
-        <v>0.6194193499999999</v>
+        <v>0.6757301999999998</v>
       </c>
       <c r="N13">
-        <v>12.14058065</v>
+        <v>12.0842698</v>
       </c>
       <c r="O13">
-        <v>2.3067103235</v>
+        <v>2.296011262</v>
       </c>
       <c r="P13">
-        <v>9.833870326500001</v>
+        <v>9.788258538000001</v>
       </c>
       <c r="Q13">
-        <v>12.3738703265</v>
+        <v>12.328258538</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07087031487505757</v>
+        <v>0.07110600158001849</v>
       </c>
       <c r="T13">
-        <v>0.4886671002674102</v>
+        <v>0.4932610728305317</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.59993766742999</v>
+        <v>18.88327619514416</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06746244139041628</v>
+        <v>0.06736857254203131</v>
       </c>
       <c r="C14">
-        <v>101.5300109786389</v>
+        <v>100.676887290227</v>
       </c>
       <c r="D14">
-        <v>92.86401097863892</v>
+        <v>93.13038729022701</v>
       </c>
       <c r="E14">
-        <v>12.584</v>
+        <v>13.7035</v>
       </c>
       <c r="F14">
-        <v>13.434</v>
+        <v>14.5535</v>
       </c>
       <c r="G14">
         <v>22.1</v>
@@ -2435,28 +2435,28 @@
         <v>12.76</v>
       </c>
       <c r="M14">
-        <v>0.6757301999999998</v>
+        <v>0.73204105</v>
       </c>
       <c r="N14">
-        <v>12.0842698</v>
+        <v>12.02795895</v>
       </c>
       <c r="O14">
-        <v>2.296011262</v>
+        <v>2.2853122005</v>
       </c>
       <c r="P14">
-        <v>9.788258538000001</v>
+        <v>9.742646749500002</v>
       </c>
       <c r="Q14">
-        <v>12.328258538</v>
+        <v>12.2826467495</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07110600158001849</v>
+        <v>0.07134710637015093</v>
       </c>
       <c r="T14">
-        <v>0.4932610728305317</v>
+        <v>0.4979606539583227</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.88327619514416</v>
+        <v>17.43071648782538</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06736857254203131</v>
+        <v>0.06727470369364634</v>
       </c>
       <c r="C15">
-        <v>100.676887290227</v>
+        <v>99.82529617529022</v>
       </c>
       <c r="D15">
-        <v>93.13038729022701</v>
+        <v>93.39829617529023</v>
       </c>
       <c r="E15">
-        <v>13.7035</v>
+        <v>14.823</v>
       </c>
       <c r="F15">
-        <v>14.5535</v>
+        <v>15.673</v>
       </c>
       <c r="G15">
         <v>22.1</v>
@@ -2517,28 +2517,28 @@
         <v>12.76</v>
       </c>
       <c r="M15">
-        <v>0.73204105</v>
+        <v>0.7883519</v>
       </c>
       <c r="N15">
-        <v>12.02795895</v>
+        <v>11.9716481</v>
       </c>
       <c r="O15">
-        <v>2.2853122005</v>
+        <v>2.274613139</v>
       </c>
       <c r="P15">
-        <v>9.742646749500002</v>
+        <v>9.697034961</v>
       </c>
       <c r="Q15">
-        <v>12.2826467495</v>
+        <v>12.237034961</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07134710637015093</v>
+        <v>0.07159381824842598</v>
       </c>
       <c r="T15">
-        <v>0.4979606539583227</v>
+        <v>0.502769527670481</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.43071648782538</v>
+        <v>16.18566531012356</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06727470369364634</v>
+        <v>0.06718083484526138</v>
       </c>
       <c r="C16">
-        <v>99.82529617529022</v>
+        <v>98.97525089828342</v>
       </c>
       <c r="D16">
-        <v>93.39829617529023</v>
+        <v>93.66775089828343</v>
       </c>
       <c r="E16">
-        <v>14.823</v>
+        <v>15.9425</v>
       </c>
       <c r="F16">
-        <v>15.673</v>
+        <v>16.7925</v>
       </c>
       <c r="G16">
         <v>22.1</v>
@@ -2599,28 +2599,28 @@
         <v>12.76</v>
       </c>
       <c r="M16">
-        <v>0.7883519</v>
+        <v>0.84466275</v>
       </c>
       <c r="N16">
-        <v>11.9716481</v>
+        <v>11.91533725</v>
       </c>
       <c r="O16">
-        <v>2.274613139</v>
+        <v>2.2639140775</v>
       </c>
       <c r="P16">
-        <v>9.697034961</v>
+        <v>9.651423172500001</v>
       </c>
       <c r="Q16">
-        <v>12.237034961</v>
+        <v>12.1914231725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07159381824842598</v>
+        <v>0.07184633511207221</v>
       </c>
       <c r="T16">
-        <v>0.502769527670481</v>
+        <v>0.5076915513523371</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.18566531012356</v>
+        <v>15.10662095611533</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06718083484526138</v>
+        <v>0.06708696599687641</v>
       </c>
       <c r="C17">
-        <v>98.97525089828343</v>
+        <v>98.12676487717653</v>
       </c>
       <c r="D17">
-        <v>93.66775089828343</v>
+        <v>93.93876487717654</v>
       </c>
       <c r="E17">
-        <v>15.9425</v>
+        <v>17.062</v>
       </c>
       <c r="F17">
-        <v>16.7925</v>
+        <v>17.912</v>
       </c>
       <c r="G17">
         <v>22.1</v>
@@ -2681,28 +2681,28 @@
         <v>12.76</v>
       </c>
       <c r="M17">
-        <v>0.8446627499999998</v>
+        <v>0.9009735999999999</v>
       </c>
       <c r="N17">
-        <v>11.91533725</v>
+        <v>11.8590264</v>
       </c>
       <c r="O17">
-        <v>2.2639140775</v>
+        <v>2.253215016</v>
       </c>
       <c r="P17">
-        <v>9.651423172500001</v>
+        <v>9.605811384000001</v>
       </c>
       <c r="Q17">
-        <v>12.1914231725</v>
+        <v>12.145811384</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07184633511207221</v>
+        <v>0.07210486428199572</v>
       </c>
       <c r="T17">
-        <v>0.5076915513523371</v>
+        <v>0.5127307660742373</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.10662095611533</v>
+        <v>14.16245714635812</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06708696599687641</v>
+        <v>0.06699309714849143</v>
       </c>
       <c r="C18">
-        <v>98.12676487717653</v>
+        <v>97.27985168568193</v>
       </c>
       <c r="D18">
-        <v>93.93876487717654</v>
+        <v>94.21135168568193</v>
       </c>
       <c r="E18">
-        <v>17.062</v>
+        <v>18.1815</v>
       </c>
       <c r="F18">
-        <v>17.912</v>
+        <v>19.0315</v>
       </c>
       <c r="G18">
         <v>22.1</v>
@@ -2763,28 +2763,28 @@
         <v>12.76</v>
       </c>
       <c r="M18">
-        <v>0.9009735999999999</v>
+        <v>0.9572844500000001</v>
       </c>
       <c r="N18">
-        <v>11.8590264</v>
+        <v>11.80271555</v>
       </c>
       <c r="O18">
-        <v>2.253215016</v>
+        <v>2.2425159545</v>
       </c>
       <c r="P18">
-        <v>9.605811384000001</v>
+        <v>9.560199595500002</v>
       </c>
       <c r="Q18">
-        <v>12.145811384</v>
+        <v>12.1001995955</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07210486428199572</v>
+        <v>0.07236962307047161</v>
       </c>
       <c r="T18">
-        <v>0.5127307660742373</v>
+        <v>0.5178914076569063</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.16245714635812</v>
+        <v>13.32937143186646</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06699309714849143</v>
+        <v>0.06711792830010647</v>
       </c>
       <c r="C19">
-        <v>97.27985168568193</v>
+        <v>95.79819872050719</v>
       </c>
       <c r="D19">
-        <v>94.21135168568193</v>
+        <v>93.84919872050719</v>
       </c>
       <c r="E19">
-        <v>18.1815</v>
+        <v>19.301</v>
       </c>
       <c r="F19">
-        <v>19.0315</v>
+        <v>20.151</v>
       </c>
       <c r="G19">
         <v>22.1</v>
@@ -2845,45 +2845,45 @@
         <v>12.76</v>
       </c>
       <c r="M19">
-        <v>0.9572844500000001</v>
+        <v>1.0438218</v>
       </c>
       <c r="N19">
-        <v>11.80271555</v>
+        <v>11.7161782</v>
       </c>
       <c r="O19">
-        <v>2.2425159545</v>
+        <v>2.226073858</v>
       </c>
       <c r="P19">
-        <v>9.560199595500002</v>
+        <v>9.490104342000002</v>
       </c>
       <c r="Q19">
-        <v>12.1001995955</v>
+        <v>12.030104342</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07236962307047161</v>
+        <v>0.07264083939037375</v>
       </c>
       <c r="T19">
-        <v>0.5178914076569063</v>
+        <v>0.5231779185464696</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.32937143186646</v>
+        <v>12.2243087852735</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06711792830010647</v>
+        <v>0.06703620945172151</v>
       </c>
       <c r="C20">
-        <v>95.79819872050719</v>
+        <v>94.91546120977773</v>
       </c>
       <c r="D20">
-        <v>93.84919872050719</v>
+        <v>94.08596120977774</v>
       </c>
       <c r="E20">
-        <v>19.30099999999999</v>
+        <v>20.4205</v>
       </c>
       <c r="F20">
-        <v>20.151</v>
+        <v>21.2705</v>
       </c>
       <c r="G20">
         <v>22.1</v>
@@ -2927,28 +2927,28 @@
         <v>12.76</v>
       </c>
       <c r="M20">
-        <v>1.0438218</v>
+        <v>1.1018119</v>
       </c>
       <c r="N20">
-        <v>11.7161782</v>
+        <v>11.6581881</v>
       </c>
       <c r="O20">
-        <v>2.226073858</v>
+        <v>2.215055739</v>
       </c>
       <c r="P20">
-        <v>9.490104342000002</v>
+        <v>9.443132361000002</v>
       </c>
       <c r="Q20">
-        <v>12.030104342</v>
+        <v>11.983132361</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07264083939037375</v>
+        <v>0.07291875240953272</v>
       </c>
       <c r="T20">
-        <v>0.5231779185464696</v>
+        <v>0.5285949605691085</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.22430878527351</v>
+        <v>11.58092411236437</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06703620945172151</v>
+        <v>0.06695449060333653</v>
       </c>
       <c r="C21">
-        <v>94.91546120977773</v>
+        <v>94.03392132788018</v>
       </c>
       <c r="D21">
-        <v>94.08596120977774</v>
+        <v>94.32392132788019</v>
       </c>
       <c r="E21">
-        <v>20.4205</v>
+        <v>21.54</v>
       </c>
       <c r="F21">
-        <v>21.2705</v>
+        <v>22.39</v>
       </c>
       <c r="G21">
         <v>22.1</v>
@@ -3009,28 +3009,28 @@
         <v>12.76</v>
       </c>
       <c r="M21">
-        <v>1.1018119</v>
+        <v>1.159802</v>
       </c>
       <c r="N21">
-        <v>11.6581881</v>
+        <v>11.600198</v>
       </c>
       <c r="O21">
-        <v>2.215055739</v>
+        <v>2.204037620000001</v>
       </c>
       <c r="P21">
-        <v>9.443132361000002</v>
+        <v>9.396160380000001</v>
       </c>
       <c r="Q21">
-        <v>11.983132361</v>
+        <v>11.93616038</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07291875240953272</v>
+        <v>0.07320361325417066</v>
       </c>
       <c r="T21">
-        <v>0.5285949605691085</v>
+        <v>0.5341474286423135</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.58092411236437</v>
+        <v>11.00187790674615</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06695449060333653</v>
+        <v>0.06687277175495157</v>
       </c>
       <c r="C22">
-        <v>94.03392132788018</v>
+        <v>93.15358818490395</v>
       </c>
       <c r="D22">
-        <v>94.32392132788019</v>
+        <v>94.56308818490396</v>
       </c>
       <c r="E22">
-        <v>21.54</v>
+        <v>22.6595</v>
       </c>
       <c r="F22">
-        <v>22.39</v>
+        <v>23.5095</v>
       </c>
       <c r="G22">
         <v>22.1</v>
@@ -3091,28 +3091,28 @@
         <v>12.76</v>
       </c>
       <c r="M22">
-        <v>1.159802</v>
+        <v>1.2177921</v>
       </c>
       <c r="N22">
-        <v>11.600198</v>
+        <v>11.5422079</v>
       </c>
       <c r="O22">
-        <v>2.204037620000001</v>
+        <v>2.193019501</v>
       </c>
       <c r="P22">
-        <v>9.396160380000001</v>
+        <v>9.349188399000001</v>
       </c>
       <c r="Q22">
-        <v>11.93616038</v>
+        <v>11.889188399</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07320361325417066</v>
+        <v>0.07349568576576147</v>
       </c>
       <c r="T22">
-        <v>0.5341474286423135</v>
+        <v>0.5398404655274982</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.00187790674615</v>
+        <v>10.47797895880586</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06687277175495157</v>
+        <v>0.0667910529065666</v>
       </c>
       <c r="C23">
-        <v>93.15358818490395</v>
+        <v>92.27447098357146</v>
       </c>
       <c r="D23">
-        <v>94.56308818490396</v>
+        <v>94.80347098357146</v>
       </c>
       <c r="E23">
-        <v>22.65949999999999</v>
+        <v>23.779</v>
       </c>
       <c r="F23">
-        <v>23.5095</v>
+        <v>24.629</v>
       </c>
       <c r="G23">
         <v>22.1</v>
@@ -3173,28 +3173,28 @@
         <v>12.76</v>
       </c>
       <c r="M23">
-        <v>1.2177921</v>
+        <v>1.2757822</v>
       </c>
       <c r="N23">
-        <v>11.5422079</v>
+        <v>11.4842178</v>
       </c>
       <c r="O23">
-        <v>2.193019501</v>
+        <v>2.182001382</v>
       </c>
       <c r="P23">
-        <v>9.349188399000001</v>
+        <v>9.302216418</v>
       </c>
       <c r="Q23">
-        <v>11.889188399</v>
+        <v>11.842216418</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07349568576576147</v>
+        <v>0.07379524731611102</v>
       </c>
       <c r="T23">
-        <v>0.5398404655274982</v>
+        <v>0.5456794777174313</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.47797895880586</v>
+        <v>10.00170718795105</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0667910529065666</v>
+        <v>0.06702604405818162</v>
       </c>
       <c r="C24">
-        <v>92.27447098357146</v>
+        <v>90.46699678450207</v>
       </c>
       <c r="D24">
-        <v>94.80347098357146</v>
+        <v>94.11549678450207</v>
       </c>
       <c r="E24">
-        <v>23.779</v>
+        <v>24.8985</v>
       </c>
       <c r="F24">
-        <v>24.629</v>
+        <v>25.7485</v>
       </c>
       <c r="G24">
         <v>22.1</v>
@@ -3255,45 +3255,45 @@
         <v>12.76</v>
       </c>
       <c r="M24">
-        <v>1.2757822</v>
+        <v>1.37754475</v>
       </c>
       <c r="N24">
-        <v>11.4842178</v>
+        <v>11.38245525</v>
       </c>
       <c r="O24">
-        <v>2.182001382</v>
+        <v>2.1626664975</v>
       </c>
       <c r="P24">
-        <v>9.302216418</v>
+        <v>9.219788752500001</v>
       </c>
       <c r="Q24">
-        <v>11.842216418</v>
+        <v>11.7597887525</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07379524731611102</v>
+        <v>0.07410258968595015</v>
       </c>
       <c r="T24">
-        <v>0.5456794777174313</v>
+        <v>0.5516701525616484</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.00170718795105</v>
+        <v>9.262856977967504</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06702604405818162</v>
+        <v>0.06695809520979666</v>
       </c>
       <c r="C25">
-        <v>90.46699678450207</v>
+        <v>89.54539956844451</v>
       </c>
       <c r="D25">
-        <v>94.11549678450207</v>
+        <v>94.31339956844451</v>
       </c>
       <c r="E25">
-        <v>24.8985</v>
+        <v>26.018</v>
       </c>
       <c r="F25">
-        <v>25.7485</v>
+        <v>26.868</v>
       </c>
       <c r="G25">
         <v>22.1</v>
@@ -3337,28 +3337,28 @@
         <v>12.76</v>
       </c>
       <c r="M25">
-        <v>1.37754475</v>
+        <v>1.437438</v>
       </c>
       <c r="N25">
-        <v>11.38245525</v>
+        <v>11.322562</v>
       </c>
       <c r="O25">
-        <v>2.1626664975</v>
+        <v>2.15128678</v>
       </c>
       <c r="P25">
-        <v>9.219788752500001</v>
+        <v>9.171275220000002</v>
       </c>
       <c r="Q25">
-        <v>11.7597887525</v>
+        <v>11.71127522</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07410258968595015</v>
+        <v>0.07441802001289034</v>
       </c>
       <c r="T25">
-        <v>0.5516701525616484</v>
+        <v>0.5578184767438713</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.262856977967504</v>
+        <v>8.876904603885524</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06695809520979666</v>
+        <v>0.06689014636141169</v>
       </c>
       <c r="C26">
-        <v>89.54539956844451</v>
+        <v>88.62463639231972</v>
       </c>
       <c r="D26">
-        <v>94.31339956844451</v>
+        <v>94.51213639231972</v>
       </c>
       <c r="E26">
-        <v>26.01799999999999</v>
+        <v>27.1375</v>
       </c>
       <c r="F26">
-        <v>26.86799999999999</v>
+        <v>27.9875</v>
       </c>
       <c r="G26">
         <v>22.1</v>
@@ -3419,28 +3419,28 @@
         <v>12.76</v>
       </c>
       <c r="M26">
-        <v>1.437438</v>
+        <v>1.49733125</v>
       </c>
       <c r="N26">
-        <v>11.322562</v>
+        <v>11.26266875</v>
       </c>
       <c r="O26">
-        <v>2.15128678</v>
+        <v>2.1399070625</v>
       </c>
       <c r="P26">
-        <v>9.171275220000002</v>
+        <v>9.122761687500001</v>
       </c>
       <c r="Q26">
-        <v>11.71127522</v>
+        <v>11.6627616875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07441802001289034</v>
+        <v>0.07474186181521558</v>
       </c>
       <c r="T26">
-        <v>0.5578184767438713</v>
+        <v>0.56413075623762</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.876904603885526</v>
+        <v>8.521828419730106</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06689014636141169</v>
+        <v>0.06682219751302673</v>
       </c>
       <c r="C27">
-        <v>88.62463639231972</v>
+        <v>87.7047125397182</v>
       </c>
       <c r="D27">
-        <v>94.51213639231972</v>
+        <v>94.71171253971819</v>
       </c>
       <c r="E27">
-        <v>27.1375</v>
+        <v>28.257</v>
       </c>
       <c r="F27">
-        <v>27.9875</v>
+        <v>29.107</v>
       </c>
       <c r="G27">
         <v>22.1</v>
@@ -3501,28 +3501,28 @@
         <v>12.76</v>
       </c>
       <c r="M27">
-        <v>1.49733125</v>
+        <v>1.5572245</v>
       </c>
       <c r="N27">
-        <v>11.26266875</v>
+        <v>11.2027755</v>
       </c>
       <c r="O27">
-        <v>2.1399070625</v>
+        <v>2.128527345</v>
       </c>
       <c r="P27">
-        <v>9.122761687500001</v>
+        <v>9.074248155000001</v>
       </c>
       <c r="Q27">
-        <v>11.6627616875</v>
+        <v>11.614248155</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07474186181521558</v>
+        <v>0.07507445609868477</v>
       </c>
       <c r="T27">
-        <v>0.56413075623762</v>
+        <v>0.5706136378798485</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.521828419730106</v>
+        <v>8.194065788202023</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06682219751302673</v>
+        <v>0.06675424866464176</v>
       </c>
       <c r="C28">
-        <v>87.7047125397182</v>
+        <v>86.78563333895325</v>
       </c>
       <c r="D28">
-        <v>94.71171253971819</v>
+        <v>94.91213333895324</v>
       </c>
       <c r="E28">
-        <v>28.257</v>
+        <v>29.3765</v>
       </c>
       <c r="F28">
-        <v>29.107</v>
+        <v>30.2265</v>
       </c>
       <c r="G28">
         <v>22.1</v>
@@ -3583,28 +3583,28 @@
         <v>12.76</v>
       </c>
       <c r="M28">
-        <v>1.5572245</v>
+        <v>1.61711775</v>
       </c>
       <c r="N28">
-        <v>11.2027755</v>
+        <v>11.14288225</v>
       </c>
       <c r="O28">
-        <v>2.128527345</v>
+        <v>2.1171476275</v>
       </c>
       <c r="P28">
-        <v>9.074248155000001</v>
+        <v>9.025734622500002</v>
       </c>
       <c r="Q28">
-        <v>11.614248155</v>
+        <v>11.5657346225</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07507445609868477</v>
+        <v>0.07541616255430378</v>
       </c>
       <c r="T28">
-        <v>0.5706136378798485</v>
+        <v>0.5772741327177544</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.194065788202023</v>
+        <v>7.890581870120467</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06675424866464176</v>
+        <v>0.06686773981625678</v>
       </c>
       <c r="C29">
-        <v>86.78563333895325</v>
+        <v>85.33185482574262</v>
       </c>
       <c r="D29">
-        <v>94.91213333895324</v>
+        <v>94.57785482574263</v>
       </c>
       <c r="E29">
-        <v>29.3765</v>
+        <v>30.496</v>
       </c>
       <c r="F29">
-        <v>30.2265</v>
+        <v>31.346</v>
       </c>
       <c r="G29">
         <v>22.1</v>
@@ -3665,45 +3665,45 @@
         <v>12.76</v>
       </c>
       <c r="M29">
-        <v>1.61711775</v>
+        <v>1.7020878</v>
       </c>
       <c r="N29">
-        <v>11.14288225</v>
+        <v>11.0579122</v>
       </c>
       <c r="O29">
-        <v>2.1171476275</v>
+        <v>2.101003318000001</v>
       </c>
       <c r="P29">
-        <v>9.025734622500002</v>
+        <v>8.956908882000002</v>
       </c>
       <c r="Q29">
-        <v>11.5657346225</v>
+        <v>11.496908882</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07541616255430378</v>
+        <v>0.07576736085591219</v>
       </c>
       <c r="T29">
-        <v>0.5772741327177544</v>
+        <v>0.5841196413011577</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.890581870120467</v>
+        <v>7.496675553399774</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06686773981625678</v>
+        <v>0.06680627096787181</v>
       </c>
       <c r="C30">
-        <v>85.33185482574262</v>
+        <v>84.39311322922282</v>
       </c>
       <c r="D30">
-        <v>94.57785482574263</v>
+        <v>94.75861322922282</v>
       </c>
       <c r="E30">
-        <v>30.496</v>
+        <v>31.6155</v>
       </c>
       <c r="F30">
-        <v>31.346</v>
+        <v>32.4655</v>
       </c>
       <c r="G30">
         <v>22.1</v>
@@ -3747,28 +3747,28 @@
         <v>12.76</v>
       </c>
       <c r="M30">
-        <v>1.7020878</v>
+        <v>1.76287665</v>
       </c>
       <c r="N30">
-        <v>11.0579122</v>
+        <v>10.99712335</v>
       </c>
       <c r="O30">
-        <v>2.101003318000001</v>
+        <v>2.0894534365</v>
       </c>
       <c r="P30">
-        <v>8.956908882000002</v>
+        <v>8.907669913500001</v>
       </c>
       <c r="Q30">
-        <v>11.496908882</v>
+        <v>11.4476699135</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07576736085591219</v>
+        <v>0.07612845206742509</v>
       </c>
       <c r="T30">
-        <v>0.5841196413011577</v>
+        <v>0.5911579811122626</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.496675553399774</v>
+        <v>7.238169499834264</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06680627096787181</v>
+        <v>0.06674480211948684</v>
       </c>
       <c r="C31">
-        <v>84.39311322922282</v>
+        <v>83.45506389129291</v>
       </c>
       <c r="D31">
-        <v>94.75861322922282</v>
+        <v>94.94006389129289</v>
       </c>
       <c r="E31">
-        <v>31.61549999999999</v>
+        <v>32.73499999999999</v>
       </c>
       <c r="F31">
-        <v>32.46549999999999</v>
+        <v>33.58499999999999</v>
       </c>
       <c r="G31">
         <v>22.1</v>
@@ -3829,28 +3829,28 @@
         <v>12.76</v>
       </c>
       <c r="M31">
-        <v>1.762876649999999</v>
+        <v>1.8236655</v>
       </c>
       <c r="N31">
-        <v>10.99712335</v>
+        <v>10.9363345</v>
       </c>
       <c r="O31">
-        <v>2.0894534365</v>
+        <v>2.077903555</v>
       </c>
       <c r="P31">
-        <v>8.907669913500001</v>
+        <v>8.858430945</v>
       </c>
       <c r="Q31">
-        <v>11.4476699135</v>
+        <v>11.398430945</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07612845206742509</v>
+        <v>0.0764998601706955</v>
       </c>
       <c r="T31">
-        <v>0.5911579811122626</v>
+        <v>0.5983974163465419</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.238169499834266</v>
+        <v>6.996897183173122</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06674480211948684</v>
+        <v>0.06668333327110189</v>
       </c>
       <c r="C32">
-        <v>83.45506389129291</v>
+        <v>82.51771079634318</v>
       </c>
       <c r="D32">
-        <v>94.94006389129289</v>
+        <v>95.12221079634317</v>
       </c>
       <c r="E32">
-        <v>32.73499999999999</v>
+        <v>33.85449999999999</v>
       </c>
       <c r="F32">
-        <v>33.58499999999999</v>
+        <v>34.7045</v>
       </c>
       <c r="G32">
         <v>22.1</v>
@@ -3911,28 +3911,28 @@
         <v>12.76</v>
       </c>
       <c r="M32">
-        <v>1.8236655</v>
+        <v>1.88445435</v>
       </c>
       <c r="N32">
-        <v>10.9363345</v>
+        <v>10.87554565</v>
       </c>
       <c r="O32">
-        <v>2.077903555</v>
+        <v>2.0663536735</v>
       </c>
       <c r="P32">
-        <v>8.858430945</v>
+        <v>8.809191976500001</v>
       </c>
       <c r="Q32">
-        <v>11.398430945</v>
+        <v>11.3491919765</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0764998601706955</v>
+        <v>0.07688203372623462</v>
       </c>
       <c r="T32">
-        <v>0.5983974163465419</v>
+        <v>0.605846690283264</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.996897183173122</v>
+        <v>6.771190822425602</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06668333327110189</v>
+        <v>0.06662186442271692</v>
       </c>
       <c r="C33">
-        <v>82.51771079634318</v>
+        <v>81.5810579593999</v>
       </c>
       <c r="D33">
-        <v>95.12221079634317</v>
+        <v>95.30505795939989</v>
       </c>
       <c r="E33">
-        <v>33.85449999999999</v>
+        <v>34.974</v>
       </c>
       <c r="F33">
-        <v>34.7045</v>
+        <v>35.824</v>
       </c>
       <c r="G33">
         <v>22.1</v>
@@ -3993,28 +3993,28 @@
         <v>12.76</v>
       </c>
       <c r="M33">
-        <v>1.88445435</v>
+        <v>1.9452432</v>
       </c>
       <c r="N33">
-        <v>10.87554565</v>
+        <v>10.8147568</v>
       </c>
       <c r="O33">
-        <v>2.0663536735</v>
+        <v>2.054803792</v>
       </c>
       <c r="P33">
-        <v>8.809191976500001</v>
+        <v>8.759953008</v>
       </c>
       <c r="Q33">
-        <v>11.3491919765</v>
+        <v>11.299953008</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07688203372623462</v>
+        <v>0.07727544768046606</v>
       </c>
       <c r="T33">
-        <v>0.605846690283264</v>
+        <v>0.6135150605122427</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.771190822425602</v>
+        <v>6.559591109224801</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06662186442271692</v>
+        <v>0.06656039557433194</v>
       </c>
       <c r="C34">
-        <v>81.5810579593999</v>
+        <v>80.64510942641991</v>
       </c>
       <c r="D34">
-        <v>95.30505795939989</v>
+        <v>95.48860942641991</v>
       </c>
       <c r="E34">
-        <v>34.974</v>
+        <v>36.0935</v>
       </c>
       <c r="F34">
-        <v>35.824</v>
+        <v>36.9435</v>
       </c>
       <c r="G34">
         <v>22.1</v>
@@ -4075,28 +4075,28 @@
         <v>12.76</v>
       </c>
       <c r="M34">
-        <v>1.9452432</v>
+        <v>2.00603205</v>
       </c>
       <c r="N34">
-        <v>10.8147568</v>
+        <v>10.75396795</v>
       </c>
       <c r="O34">
-        <v>2.054803792</v>
+        <v>2.0432539105</v>
       </c>
       <c r="P34">
-        <v>8.759953008</v>
+        <v>8.710714039500001</v>
       </c>
       <c r="Q34">
-        <v>11.299953008</v>
+        <v>11.2507140395</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07727544768046606</v>
+        <v>0.07768060533482379</v>
       </c>
       <c r="T34">
-        <v>0.6135150605122427</v>
+        <v>0.6214123373152207</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.559591109224801</v>
+        <v>6.360815621066473</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06656039557433194</v>
+        <v>0.06649892672594697</v>
       </c>
       <c r="C35">
-        <v>80.64510942641991</v>
+        <v>79.7098692745892</v>
       </c>
       <c r="D35">
-        <v>95.48860942641991</v>
+        <v>95.67286927458919</v>
       </c>
       <c r="E35">
-        <v>36.0935</v>
+        <v>37.213</v>
       </c>
       <c r="F35">
-        <v>36.9435</v>
+        <v>38.063</v>
       </c>
       <c r="G35">
         <v>22.1</v>
@@ -4157,28 +4157,28 @@
         <v>12.76</v>
       </c>
       <c r="M35">
-        <v>2.00603205</v>
+        <v>2.0668209</v>
       </c>
       <c r="N35">
-        <v>10.75396795</v>
+        <v>10.6931791</v>
       </c>
       <c r="O35">
-        <v>2.0432539105</v>
+        <v>2.031704029000001</v>
       </c>
       <c r="P35">
-        <v>8.710714039500001</v>
+        <v>8.661475071000002</v>
       </c>
       <c r="Q35">
-        <v>11.2507140395</v>
+        <v>11.201475071</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07768060533482379</v>
+        <v>0.07809804049385906</v>
       </c>
       <c r="T35">
-        <v>0.6214123373152207</v>
+        <v>0.6295489255364708</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.360815621066473</v>
+        <v>6.173732808682165</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06649892672594697</v>
+        <v>0.06672095787756201</v>
       </c>
       <c r="C36">
-        <v>79.7098692745892</v>
+        <v>77.92813720901074</v>
       </c>
       <c r="D36">
-        <v>95.67286927458919</v>
+        <v>95.01063720901075</v>
       </c>
       <c r="E36">
-        <v>37.213</v>
+        <v>38.3325</v>
       </c>
       <c r="F36">
-        <v>38.063</v>
+        <v>39.1825</v>
       </c>
       <c r="G36">
         <v>22.1</v>
@@ -4239,45 +4239,45 @@
         <v>12.76</v>
       </c>
       <c r="M36">
-        <v>2.0668209</v>
+        <v>2.16679225</v>
       </c>
       <c r="N36">
-        <v>10.6931791</v>
+        <v>10.59320775</v>
       </c>
       <c r="O36">
-        <v>2.031704029000001</v>
+        <v>2.0127094725</v>
       </c>
       <c r="P36">
-        <v>8.661475071000002</v>
+        <v>8.580498277500002</v>
       </c>
       <c r="Q36">
-        <v>11.201475071</v>
+        <v>11.1204982775</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07809804049385906</v>
+        <v>0.07852831981163386</v>
       </c>
       <c r="T36">
-        <v>0.6295489255364708</v>
+        <v>0.6379358703183746</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.173732808682165</v>
+        <v>5.88888944013899</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06672095787756201</v>
+        <v>0.06666758902917705</v>
       </c>
       <c r="C37">
-        <v>77.92813720901074</v>
+        <v>76.96697724120258</v>
       </c>
       <c r="D37">
-        <v>95.01063720901075</v>
+        <v>95.16897724120257</v>
       </c>
       <c r="E37">
-        <v>38.3325</v>
+        <v>39.452</v>
       </c>
       <c r="F37">
-        <v>39.1825</v>
+        <v>40.302</v>
       </c>
       <c r="G37">
         <v>22.1</v>
@@ -4321,28 +4321,28 @@
         <v>12.76</v>
       </c>
       <c r="M37">
-        <v>2.16679225</v>
+        <v>2.2287006</v>
       </c>
       <c r="N37">
-        <v>10.59320775</v>
+        <v>10.5312994</v>
       </c>
       <c r="O37">
-        <v>2.0127094725</v>
+        <v>2.000946886</v>
       </c>
       <c r="P37">
-        <v>8.580498277500002</v>
+        <v>8.530352514</v>
       </c>
       <c r="Q37">
-        <v>11.1204982775</v>
+        <v>11.070352514</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07852831981163386</v>
+        <v>0.07897204535808913</v>
       </c>
       <c r="T37">
-        <v>0.6379358703183746</v>
+        <v>0.6465849071247132</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.88888944013899</v>
+        <v>5.725309177912906</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06666758902917705</v>
+        <v>0.06661422018079208</v>
       </c>
       <c r="C38">
-        <v>76.96697724120258</v>
+        <v>76.00634591775078</v>
       </c>
       <c r="D38">
-        <v>95.16897724120257</v>
+        <v>95.32784591775076</v>
       </c>
       <c r="E38">
-        <v>39.45199999999999</v>
+        <v>40.57149999999999</v>
       </c>
       <c r="F38">
-        <v>40.30199999999999</v>
+        <v>41.42149999999999</v>
       </c>
       <c r="G38">
         <v>22.1</v>
@@ -4403,28 +4403,28 @@
         <v>12.76</v>
       </c>
       <c r="M38">
-        <v>2.2287006</v>
+        <v>2.29060895</v>
       </c>
       <c r="N38">
-        <v>10.5312994</v>
+        <v>10.46939105</v>
       </c>
       <c r="O38">
-        <v>2.000946886</v>
+        <v>1.9891842995</v>
       </c>
       <c r="P38">
-        <v>8.530352514</v>
+        <v>8.480206750500002</v>
       </c>
       <c r="Q38">
-        <v>11.070352514</v>
+        <v>11.0202067505</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07897204535808913</v>
+        <v>0.07942985742982869</v>
       </c>
       <c r="T38">
-        <v>0.6465849071247131</v>
+        <v>0.6555085165280782</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.725309177912907</v>
+        <v>5.57057109202337</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06661422018079208</v>
+        <v>0.06656085133240711</v>
       </c>
       <c r="C39">
-        <v>76.00634591775078</v>
+        <v>75.04624589053196</v>
       </c>
       <c r="D39">
-        <v>95.32784591775076</v>
+        <v>95.48724589053197</v>
       </c>
       <c r="E39">
-        <v>40.57149999999999</v>
+        <v>41.691</v>
       </c>
       <c r="F39">
-        <v>41.42149999999999</v>
+        <v>42.541</v>
       </c>
       <c r="G39">
         <v>22.1</v>
@@ -4485,28 +4485,28 @@
         <v>12.76</v>
       </c>
       <c r="M39">
-        <v>2.29060895</v>
+        <v>2.3525173</v>
       </c>
       <c r="N39">
-        <v>10.46939105</v>
+        <v>10.4074827</v>
       </c>
       <c r="O39">
-        <v>1.9891842995</v>
+        <v>1.977421713</v>
       </c>
       <c r="P39">
-        <v>8.480206750500002</v>
+        <v>8.430060987000003</v>
       </c>
       <c r="Q39">
-        <v>11.0202067505</v>
+        <v>10.970060987</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07942985742982869</v>
+        <v>0.07990243763291469</v>
       </c>
       <c r="T39">
-        <v>0.6555085165280782</v>
+        <v>0.6647199842992937</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.57057109202337</v>
+        <v>5.423977115917491</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06656085133240711</v>
+        <v>0.06650748248402213</v>
       </c>
       <c r="C40">
-        <v>75.04624589053196</v>
+        <v>74.08667982918955</v>
       </c>
       <c r="D40">
-        <v>95.48724589053197</v>
+        <v>95.64717982918955</v>
       </c>
       <c r="E40">
-        <v>41.691</v>
+        <v>42.8105</v>
       </c>
       <c r="F40">
-        <v>42.541</v>
+        <v>43.6605</v>
       </c>
       <c r="G40">
         <v>22.1</v>
@@ -4567,28 +4567,28 @@
         <v>12.76</v>
       </c>
       <c r="M40">
-        <v>2.3525173</v>
+        <v>2.41442565</v>
       </c>
       <c r="N40">
-        <v>10.4074827</v>
+        <v>10.34557435</v>
       </c>
       <c r="O40">
-        <v>1.977421713</v>
+        <v>1.9656591265</v>
       </c>
       <c r="P40">
-        <v>8.430060987000003</v>
+        <v>8.379915223500001</v>
       </c>
       <c r="Q40">
-        <v>10.970060987</v>
+        <v>10.9199152235</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07990243763291469</v>
+        <v>0.08039051226888874</v>
       </c>
       <c r="T40">
-        <v>0.6647199842992937</v>
+        <v>0.6742334674072704</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.423977115917491</v>
+        <v>5.284900779611913</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06650748248402213</v>
+        <v>0.06645411363563718</v>
       </c>
       <c r="C41">
-        <v>74.08667982918955</v>
+        <v>73.12765042128274</v>
       </c>
       <c r="D41">
-        <v>95.64717982918955</v>
+        <v>95.80765042128274</v>
       </c>
       <c r="E41">
-        <v>42.8105</v>
+        <v>43.93</v>
       </c>
       <c r="F41">
-        <v>43.6605</v>
+        <v>44.78</v>
       </c>
       <c r="G41">
         <v>22.1</v>
@@ -4649,28 +4649,28 @@
         <v>12.76</v>
       </c>
       <c r="M41">
-        <v>2.41442565</v>
+        <v>2.476334</v>
       </c>
       <c r="N41">
-        <v>10.34557435</v>
+        <v>10.283666</v>
       </c>
       <c r="O41">
-        <v>1.9656591265</v>
+        <v>1.95389654</v>
       </c>
       <c r="P41">
-        <v>8.379915223500001</v>
+        <v>8.329769460000001</v>
       </c>
       <c r="Q41">
-        <v>10.9199152235</v>
+        <v>10.86976946</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08039051226888874</v>
+        <v>0.08089485605939528</v>
       </c>
       <c r="T41">
-        <v>0.6742334674072704</v>
+        <v>0.6840640666188463</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.284900779611913</v>
+        <v>5.152778260121616</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06645411363563718</v>
+        <v>0.06640074478725219</v>
       </c>
       <c r="C42">
-        <v>73.12765042128274</v>
+        <v>72.16916037243726</v>
       </c>
       <c r="D42">
-        <v>95.80765042128274</v>
+        <v>95.96866037243726</v>
       </c>
       <c r="E42">
-        <v>43.93</v>
+        <v>45.04949999999999</v>
       </c>
       <c r="F42">
-        <v>44.78</v>
+        <v>45.8995</v>
       </c>
       <c r="G42">
         <v>22.1</v>
@@ -4731,28 +4731,28 @@
         <v>12.76</v>
       </c>
       <c r="M42">
-        <v>2.476334</v>
+        <v>2.53824235</v>
       </c>
       <c r="N42">
-        <v>10.283666</v>
+        <v>10.22175765</v>
       </c>
       <c r="O42">
-        <v>1.95389654</v>
+        <v>1.9421339535</v>
       </c>
       <c r="P42">
-        <v>8.329769460000001</v>
+        <v>8.2796236965</v>
       </c>
       <c r="Q42">
-        <v>10.86976946</v>
+        <v>10.8196236965</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08089485605939528</v>
+        <v>0.08141629624957999</v>
       </c>
       <c r="T42">
-        <v>0.6840640666188463</v>
+        <v>0.6942279064816621</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.152778260121616</v>
+        <v>5.027100741582064</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06640074478725219</v>
+        <v>0.06634737593886723</v>
       </c>
       <c r="C43">
-        <v>72.16916037243726</v>
+        <v>71.21121240649688</v>
       </c>
       <c r="D43">
-        <v>95.96866037243726</v>
+        <v>96.1302124064969</v>
       </c>
       <c r="E43">
-        <v>45.04949999999999</v>
+        <v>46.169</v>
       </c>
       <c r="F43">
-        <v>45.8995</v>
+        <v>47.019</v>
       </c>
       <c r="G43">
         <v>22.1</v>
@@ -4813,28 +4813,28 @@
         <v>12.76</v>
       </c>
       <c r="M43">
-        <v>2.53824235</v>
+        <v>2.6001507</v>
       </c>
       <c r="N43">
-        <v>10.22175765</v>
+        <v>10.1598493</v>
       </c>
       <c r="O43">
-        <v>1.9421339535</v>
+        <v>1.930371367</v>
       </c>
       <c r="P43">
-        <v>8.2796236965</v>
+        <v>8.229477933000002</v>
       </c>
       <c r="Q43">
-        <v>10.8196236965</v>
+        <v>10.769477933</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08141629624957999</v>
+        <v>0.08195571713597799</v>
       </c>
       <c r="T43">
-        <v>0.6942279064816621</v>
+        <v>0.7047422235811268</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.027100741582064</v>
+        <v>4.907407866782491</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06634737593886725</v>
+        <v>0.06629400709048226</v>
       </c>
       <c r="C44">
-        <v>71.21121240649684</v>
+        <v>70.25380926567786</v>
       </c>
       <c r="D44">
-        <v>96.13021240649684</v>
+        <v>96.29230926567784</v>
       </c>
       <c r="E44">
-        <v>46.16899999999999</v>
+        <v>47.28849999999999</v>
       </c>
       <c r="F44">
-        <v>47.01899999999999</v>
+        <v>48.13849999999999</v>
       </c>
       <c r="G44">
         <v>22.1</v>
@@ -4895,28 +4895,28 @@
         <v>12.76</v>
       </c>
       <c r="M44">
-        <v>2.600150699999999</v>
+        <v>2.66205905</v>
       </c>
       <c r="N44">
-        <v>10.1598493</v>
+        <v>10.09794095</v>
       </c>
       <c r="O44">
-        <v>1.930371367</v>
+        <v>1.9186087805</v>
       </c>
       <c r="P44">
-        <v>8.229477933000002</v>
+        <v>8.179332169500002</v>
       </c>
       <c r="Q44">
-        <v>10.769477933</v>
+        <v>10.7193321695</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08195571713597799</v>
+        <v>0.08251406507102151</v>
       </c>
       <c r="T44">
-        <v>0.7047422235811267</v>
+        <v>0.71562546408759</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.907407866782492</v>
+        <v>4.793282102438713</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06629400709048226</v>
+        <v>0.0662406382420973</v>
       </c>
       <c r="C45">
-        <v>70.25380926567786</v>
+        <v>69.2969537107232</v>
       </c>
       <c r="D45">
-        <v>96.29230926567784</v>
+        <v>96.4549537107232</v>
       </c>
       <c r="E45">
-        <v>47.28849999999999</v>
+        <v>48.40799999999999</v>
       </c>
       <c r="F45">
-        <v>48.13849999999999</v>
+        <v>49.258</v>
       </c>
       <c r="G45">
         <v>22.1</v>
@@ -4977,28 +4977,28 @@
         <v>12.76</v>
       </c>
       <c r="M45">
-        <v>2.66205905</v>
+        <v>2.7239674</v>
       </c>
       <c r="N45">
-        <v>10.09794095</v>
+        <v>10.0360326</v>
       </c>
       <c r="O45">
-        <v>1.9186087805</v>
+        <v>1.906846194000001</v>
       </c>
       <c r="P45">
-        <v>8.179332169500002</v>
+        <v>8.129186406000002</v>
       </c>
       <c r="Q45">
-        <v>10.7193321695</v>
+        <v>10.669186406</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08251406507102151</v>
+        <v>0.08309235400374518</v>
       </c>
       <c r="T45">
-        <v>0.71562546408759</v>
+        <v>0.7268973917549986</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.793282102438713</v>
+        <v>4.684343872837833</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0662406382420973</v>
+        <v>0.06618726939371233</v>
       </c>
       <c r="C46">
-        <v>69.2969537107232</v>
+        <v>68.34064852106019</v>
       </c>
       <c r="D46">
-        <v>96.4549537107232</v>
+        <v>96.61814852106018</v>
       </c>
       <c r="E46">
-        <v>48.40799999999999</v>
+        <v>49.5275</v>
       </c>
       <c r="F46">
-        <v>49.258</v>
+        <v>50.3775</v>
       </c>
       <c r="G46">
         <v>22.1</v>
@@ -5059,28 +5059,28 @@
         <v>12.76</v>
       </c>
       <c r="M46">
-        <v>2.7239674</v>
+        <v>2.78587575</v>
       </c>
       <c r="N46">
-        <v>10.0360326</v>
+        <v>9.974124250000003</v>
       </c>
       <c r="O46">
-        <v>1.906846194000001</v>
+        <v>1.895083607500001</v>
       </c>
       <c r="P46">
-        <v>8.129186406000002</v>
+        <v>8.079040642500003</v>
       </c>
       <c r="Q46">
-        <v>10.669186406</v>
+        <v>10.6190406425</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08309235400374518</v>
+        <v>0.08369167162493149</v>
       </c>
       <c r="T46">
-        <v>0.7268973917549986</v>
+        <v>0.7385792077012219</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.684343872837833</v>
+        <v>4.580247342330326</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06618726939371233</v>
+        <v>0.06706540054532736</v>
       </c>
       <c r="C47">
-        <v>68.34064852106019</v>
+        <v>64.60424937619949</v>
       </c>
       <c r="D47">
-        <v>96.61814852106018</v>
+        <v>94.00124937619948</v>
       </c>
       <c r="E47">
-        <v>49.5275</v>
+        <v>50.647</v>
       </c>
       <c r="F47">
-        <v>50.3775</v>
+        <v>51.497</v>
       </c>
       <c r="G47">
         <v>22.1</v>
@@ -5141,45 +5141,45 @@
         <v>12.76</v>
       </c>
       <c r="M47">
-        <v>2.78587575</v>
+        <v>2.9765266</v>
       </c>
       <c r="N47">
-        <v>9.974124250000003</v>
+        <v>9.783473400000002</v>
       </c>
       <c r="O47">
-        <v>1.895083607500001</v>
+        <v>1.858859946</v>
       </c>
       <c r="P47">
-        <v>8.079040642500003</v>
+        <v>7.924613454000001</v>
       </c>
       <c r="Q47">
-        <v>10.6190406425</v>
+        <v>10.464613454</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08369167162493149</v>
+        <v>0.08431318619505065</v>
       </c>
       <c r="T47">
-        <v>0.7385792077012219</v>
+        <v>0.7506936834973054</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.19</v>
       </c>
       <c r="W47">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.580247342330326</v>
+        <v>4.286875850529944</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06706540054532736</v>
+        <v>0.06703228169694239</v>
       </c>
       <c r="C48">
-        <v>64.60424937619949</v>
+        <v>63.58087111262953</v>
       </c>
       <c r="D48">
-        <v>94.00124937619948</v>
+        <v>94.09737111262953</v>
       </c>
       <c r="E48">
-        <v>50.647</v>
+        <v>51.76649999999999</v>
       </c>
       <c r="F48">
-        <v>51.497</v>
+        <v>52.61649999999999</v>
       </c>
       <c r="G48">
         <v>22.1</v>
@@ -5223,28 +5223,28 @@
         <v>12.76</v>
       </c>
       <c r="M48">
-        <v>2.9765266</v>
+        <v>3.0412337</v>
       </c>
       <c r="N48">
-        <v>9.783473400000002</v>
+        <v>9.718766300000002</v>
       </c>
       <c r="O48">
-        <v>1.858859946</v>
+        <v>1.846565597</v>
       </c>
       <c r="P48">
-        <v>7.924613454000001</v>
+        <v>7.872200703000002</v>
       </c>
       <c r="Q48">
-        <v>10.464613454</v>
+        <v>10.412200703</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08431318619505065</v>
+        <v>0.08495815414517432</v>
       </c>
       <c r="T48">
-        <v>0.7506936834973054</v>
+        <v>0.7632653093234297</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.286875850529944</v>
+        <v>4.195665726050583</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06703228169694239</v>
+        <v>0.06699916284855743</v>
       </c>
       <c r="C49">
-        <v>63.58087111262953</v>
+        <v>62.55768963039508</v>
       </c>
       <c r="D49">
-        <v>94.09737111262953</v>
+        <v>94.19368963039507</v>
       </c>
       <c r="E49">
-        <v>51.76649999999999</v>
+        <v>52.886</v>
       </c>
       <c r="F49">
-        <v>52.61649999999999</v>
+        <v>53.736</v>
       </c>
       <c r="G49">
         <v>22.1</v>
@@ -5305,28 +5305,28 @@
         <v>12.76</v>
       </c>
       <c r="M49">
-        <v>3.0412337</v>
+        <v>3.1059408</v>
       </c>
       <c r="N49">
-        <v>9.718766300000002</v>
+        <v>9.654059200000003</v>
       </c>
       <c r="O49">
-        <v>1.846565597</v>
+        <v>1.834271248000001</v>
       </c>
       <c r="P49">
-        <v>7.872200703000002</v>
+        <v>7.819787952000002</v>
       </c>
       <c r="Q49">
-        <v>10.412200703</v>
+        <v>10.359787952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08495815414517432</v>
+        <v>0.08562792855491812</v>
       </c>
       <c r="T49">
-        <v>0.7632653093234297</v>
+        <v>0.7763204592197896</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.195665726050583</v>
+        <v>4.10825602342453</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06699916284855742</v>
+        <v>0.06696604400017245</v>
       </c>
       <c r="C50">
-        <v>62.55768963039512</v>
+        <v>61.53470553439429</v>
       </c>
       <c r="D50">
-        <v>94.1936896303951</v>
+        <v>94.29020553439429</v>
       </c>
       <c r="E50">
-        <v>52.88599999999999</v>
+        <v>54.00549999999999</v>
       </c>
       <c r="F50">
-        <v>53.73599999999999</v>
+        <v>54.85549999999999</v>
       </c>
       <c r="G50">
         <v>22.1</v>
@@ -5387,28 +5387,28 @@
         <v>12.76</v>
       </c>
       <c r="M50">
-        <v>3.1059408</v>
+        <v>3.1706479</v>
       </c>
       <c r="N50">
-        <v>9.654059200000003</v>
+        <v>9.589352100000003</v>
       </c>
       <c r="O50">
-        <v>1.834271248000001</v>
+        <v>1.821976899</v>
       </c>
       <c r="P50">
-        <v>7.819787952000002</v>
+        <v>7.767375201000002</v>
       </c>
       <c r="Q50">
-        <v>10.359787952</v>
+        <v>10.307375201</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0856279285549181</v>
+        <v>0.08632396862778913</v>
       </c>
       <c r="T50">
-        <v>0.7763204592197895</v>
+        <v>0.7898875757787519</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.108256023424531</v>
+        <v>4.024414063762805</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06696604400017245</v>
+        <v>0.06835042515178749</v>
       </c>
       <c r="C51">
-        <v>61.53470553439429</v>
+        <v>56.54253810870151</v>
       </c>
       <c r="D51">
-        <v>94.29020553439429</v>
+        <v>90.41753810870149</v>
       </c>
       <c r="E51">
-        <v>54.00549999999999</v>
+        <v>55.12499999999999</v>
       </c>
       <c r="F51">
-        <v>54.85549999999999</v>
+        <v>55.97499999999999</v>
       </c>
       <c r="G51">
         <v>22.1</v>
@@ -5469,45 +5469,45 @@
         <v>12.76</v>
       </c>
       <c r="M51">
-        <v>3.1706479</v>
+        <v>3.4312675</v>
       </c>
       <c r="N51">
-        <v>9.589352100000003</v>
+        <v>9.328732500000001</v>
       </c>
       <c r="O51">
-        <v>1.821976899</v>
+        <v>1.772459175</v>
       </c>
       <c r="P51">
-        <v>7.767375201000002</v>
+        <v>7.556273325000001</v>
       </c>
       <c r="Q51">
-        <v>10.307375201</v>
+        <v>10.096273325</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08632396862778913</v>
+        <v>0.08704785030357498</v>
       </c>
       <c r="T51">
-        <v>0.7898875757787519</v>
+        <v>0.8039973770000727</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.024414063762805</v>
+        <v>3.718742418071457</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06835042515178749</v>
+        <v>0.06834565630340252</v>
       </c>
       <c r="C52">
-        <v>56.54253810870151</v>
+        <v>55.43583238085922</v>
       </c>
       <c r="D52">
-        <v>90.41753810870149</v>
+        <v>90.43033238085923</v>
       </c>
       <c r="E52">
-        <v>55.12499999999999</v>
+        <v>56.2445</v>
       </c>
       <c r="F52">
-        <v>55.97499999999999</v>
+        <v>57.0945</v>
       </c>
       <c r="G52">
         <v>22.1</v>
@@ -5551,28 +5551,28 @@
         <v>12.76</v>
       </c>
       <c r="M52">
-        <v>3.4312675</v>
+        <v>3.49989285</v>
       </c>
       <c r="N52">
-        <v>9.328732500000001</v>
+        <v>9.260107150000001</v>
       </c>
       <c r="O52">
-        <v>1.772459175</v>
+        <v>1.7594203585</v>
       </c>
       <c r="P52">
-        <v>7.556273325000001</v>
+        <v>7.500686791500002</v>
       </c>
       <c r="Q52">
-        <v>10.096273325</v>
+        <v>10.0406867915</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08704785030357498</v>
+        <v>0.08780127817020922</v>
       </c>
       <c r="T52">
-        <v>0.8039973770000727</v>
+        <v>0.8186830884753249</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.718742418071457</v>
+        <v>3.645825900070056</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06834565630340252</v>
+        <v>0.06834088745501755</v>
       </c>
       <c r="C53">
-        <v>55.43583238085922</v>
+        <v>54.32913027436231</v>
       </c>
       <c r="D53">
-        <v>90.43033238085923</v>
+        <v>90.4431302743623</v>
       </c>
       <c r="E53">
-        <v>56.2445</v>
+        <v>57.364</v>
       </c>
       <c r="F53">
-        <v>57.0945</v>
+        <v>58.214</v>
       </c>
       <c r="G53">
         <v>22.1</v>
@@ -5633,28 +5633,28 @@
         <v>12.76</v>
       </c>
       <c r="M53">
-        <v>3.49989285</v>
+        <v>3.5685182</v>
       </c>
       <c r="N53">
-        <v>9.260107150000001</v>
+        <v>9.191481800000002</v>
       </c>
       <c r="O53">
-        <v>1.7594203585</v>
+        <v>1.746381542</v>
       </c>
       <c r="P53">
-        <v>7.500686791500002</v>
+        <v>7.445100258000002</v>
       </c>
       <c r="Q53">
-        <v>10.0406867915</v>
+        <v>9.985100258000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08780127817020922</v>
+        <v>0.08858609886461989</v>
       </c>
       <c r="T53">
-        <v>0.8186830884753249</v>
+        <v>0.8339807045953792</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.645825900070056</v>
+        <v>3.575713863530247</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06834088745501755</v>
+        <v>0.06833611860663259</v>
       </c>
       <c r="C54">
-        <v>54.32913027436231</v>
+        <v>53.22243179074845</v>
       </c>
       <c r="D54">
-        <v>90.4431302743623</v>
+        <v>90.45593179074845</v>
       </c>
       <c r="E54">
-        <v>57.364</v>
+        <v>58.48349999999999</v>
       </c>
       <c r="F54">
-        <v>58.214</v>
+        <v>59.33349999999999</v>
       </c>
       <c r="G54">
         <v>22.1</v>
@@ -5715,28 +5715,28 @@
         <v>12.76</v>
       </c>
       <c r="M54">
-        <v>3.5685182</v>
+        <v>3.63714355</v>
       </c>
       <c r="N54">
-        <v>9.191481800000002</v>
+        <v>9.122856450000002</v>
       </c>
       <c r="O54">
-        <v>1.746381542</v>
+        <v>1.7333427255</v>
       </c>
       <c r="P54">
-        <v>7.445100258000002</v>
+        <v>7.389513724500002</v>
       </c>
       <c r="Q54">
-        <v>9.985100258000003</v>
+        <v>9.929513724500001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08858609886461989</v>
+        <v>0.08940431618432465</v>
       </c>
       <c r="T54">
-        <v>0.8339807045953792</v>
+        <v>0.8499292831035211</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.575713863530247</v>
+        <v>3.508247564218355</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06833611860663259</v>
+        <v>0.06955606975824763</v>
       </c>
       <c r="C55">
-        <v>53.22243179074845</v>
+        <v>48.94207724557157</v>
       </c>
       <c r="D55">
-        <v>90.45593179074845</v>
+        <v>87.29507724557158</v>
       </c>
       <c r="E55">
-        <v>58.48349999999999</v>
+        <v>59.60299999999999</v>
       </c>
       <c r="F55">
-        <v>59.33349999999999</v>
+        <v>60.453</v>
       </c>
       <c r="G55">
         <v>22.1</v>
@@ -5797,45 +5797,45 @@
         <v>12.76</v>
       </c>
       <c r="M55">
-        <v>3.63714355</v>
+        <v>3.8750373</v>
       </c>
       <c r="N55">
-        <v>9.122856450000002</v>
+        <v>8.884962700000003</v>
       </c>
       <c r="O55">
-        <v>1.7333427255</v>
+        <v>1.688142913000001</v>
       </c>
       <c r="P55">
-        <v>7.389513724500002</v>
+        <v>7.196819787000003</v>
       </c>
       <c r="Q55">
-        <v>9.929513724500001</v>
+        <v>9.736819787000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08940431618432465</v>
+        <v>0.09025810817010352</v>
       </c>
       <c r="T55">
-        <v>0.8499292831035211</v>
+        <v>0.8665712780685386</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.508247564218355</v>
+        <v>3.292871529262442</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06955606975824763</v>
+        <v>0.06957398090986264</v>
       </c>
       <c r="C56">
-        <v>48.94207724557157</v>
+        <v>47.77781462230765</v>
       </c>
       <c r="D56">
-        <v>87.29507724557158</v>
+        <v>87.25031462230764</v>
       </c>
       <c r="E56">
-        <v>59.60299999999999</v>
+        <v>60.7225</v>
       </c>
       <c r="F56">
-        <v>60.453</v>
+        <v>61.5725</v>
       </c>
       <c r="G56">
         <v>22.1</v>
@@ -5879,28 +5879,28 @@
         <v>12.76</v>
       </c>
       <c r="M56">
-        <v>3.8750373</v>
+        <v>3.94679725</v>
       </c>
       <c r="N56">
-        <v>8.884962700000003</v>
+        <v>8.813202750000002</v>
       </c>
       <c r="O56">
-        <v>1.688142913000001</v>
+        <v>1.6745085225</v>
       </c>
       <c r="P56">
-        <v>7.196819787000003</v>
+        <v>7.138694227500002</v>
       </c>
       <c r="Q56">
-        <v>9.736819787000002</v>
+        <v>9.678694227500003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09025810817010352</v>
+        <v>0.09114984646636143</v>
       </c>
       <c r="T56">
-        <v>0.8665712780685386</v>
+        <v>0.8839529172542235</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.292871529262442</v>
+        <v>3.233001137821306</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06957398090986264</v>
+        <v>0.06959189206147767</v>
       </c>
       <c r="C57">
-        <v>47.77781462230765</v>
+        <v>46.61359788171172</v>
       </c>
       <c r="D57">
-        <v>87.25031462230764</v>
+        <v>87.20559788171172</v>
       </c>
       <c r="E57">
-        <v>60.7225</v>
+        <v>61.842</v>
       </c>
       <c r="F57">
-        <v>61.5725</v>
+        <v>62.692</v>
       </c>
       <c r="G57">
         <v>22.1</v>
@@ -5961,28 +5961,28 @@
         <v>12.76</v>
       </c>
       <c r="M57">
-        <v>3.94679725</v>
+        <v>4.0185572</v>
       </c>
       <c r="N57">
-        <v>8.813202750000002</v>
+        <v>8.741442800000002</v>
       </c>
       <c r="O57">
-        <v>1.6745085225</v>
+        <v>1.660874132</v>
       </c>
       <c r="P57">
-        <v>7.138694227500002</v>
+        <v>7.080568668000002</v>
       </c>
       <c r="Q57">
-        <v>9.678694227500003</v>
+        <v>9.620568668000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09114984646636143</v>
+        <v>0.09208211832154017</v>
       </c>
       <c r="T57">
-        <v>0.8839529172542235</v>
+        <v>0.9021246309483488</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.233001137821306</v>
+        <v>3.175268974645926</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06959189206147767</v>
+        <v>0.06960980321309271</v>
       </c>
       <c r="C58">
-        <v>46.61359788171172</v>
+        <v>45.44942695327392</v>
       </c>
       <c r="D58">
-        <v>87.20559788171172</v>
+        <v>87.16092695327391</v>
       </c>
       <c r="E58">
-        <v>61.842</v>
+        <v>62.9615</v>
       </c>
       <c r="F58">
-        <v>62.692</v>
+        <v>63.8115</v>
       </c>
       <c r="G58">
         <v>22.1</v>
@@ -6043,28 +6043,28 @@
         <v>12.76</v>
       </c>
       <c r="M58">
-        <v>4.0185572</v>
+        <v>4.090317150000001</v>
       </c>
       <c r="N58">
-        <v>8.741442800000002</v>
+        <v>8.669682850000001</v>
       </c>
       <c r="O58">
-        <v>1.660874132</v>
+        <v>1.6472397415</v>
       </c>
       <c r="P58">
-        <v>7.080568668000002</v>
+        <v>7.022443108500001</v>
       </c>
       <c r="Q58">
-        <v>9.620568668000001</v>
+        <v>9.562443108500002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09208211832154017</v>
+        <v>0.09305775165835514</v>
       </c>
       <c r="T58">
-        <v>0.9021246309483488</v>
+        <v>0.9211415406282472</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.175268974645926</v>
+        <v>3.119562501406523</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06960980321309271</v>
+        <v>0.06962771436470774</v>
       </c>
       <c r="C59">
-        <v>45.44942695327392</v>
+        <v>44.28530176662865</v>
       </c>
       <c r="D59">
-        <v>87.16092695327391</v>
+        <v>87.11630176662865</v>
       </c>
       <c r="E59">
-        <v>62.9615</v>
+        <v>64.081</v>
       </c>
       <c r="F59">
-        <v>63.8115</v>
+        <v>64.931</v>
       </c>
       <c r="G59">
         <v>22.1</v>
@@ -6125,28 +6125,28 @@
         <v>12.76</v>
       </c>
       <c r="M59">
-        <v>4.090317150000001</v>
+        <v>4.1620771</v>
       </c>
       <c r="N59">
-        <v>8.669682850000001</v>
+        <v>8.5979229</v>
       </c>
       <c r="O59">
-        <v>1.6472397415</v>
+        <v>1.633605351</v>
       </c>
       <c r="P59">
-        <v>7.022443108500001</v>
+        <v>6.964317549</v>
       </c>
       <c r="Q59">
-        <v>9.562443108500002</v>
+        <v>9.504317549</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09305775165835514</v>
+        <v>0.09407984372549463</v>
       </c>
       <c r="T59">
-        <v>0.9211415406282472</v>
+        <v>0.9410640174357601</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.119562501406523</v>
+        <v>3.065776941037445</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06962771436470774</v>
+        <v>0.06964562551632278</v>
       </c>
       <c r="C60">
-        <v>44.28530176662866</v>
+        <v>43.12122225155439</v>
       </c>
       <c r="D60">
-        <v>87.11630176662865</v>
+        <v>87.07172225155438</v>
       </c>
       <c r="E60">
-        <v>64.08099999999999</v>
+        <v>65.20049999999999</v>
       </c>
       <c r="F60">
-        <v>64.93099999999998</v>
+        <v>66.05049999999999</v>
       </c>
       <c r="G60">
         <v>22.1</v>
@@ -6207,28 +6207,28 @@
         <v>12.76</v>
       </c>
       <c r="M60">
-        <v>4.162077099999999</v>
+        <v>4.233837049999999</v>
       </c>
       <c r="N60">
-        <v>8.597922900000002</v>
+        <v>8.526162950000003</v>
       </c>
       <c r="O60">
-        <v>1.633605351</v>
+        <v>1.619970960500001</v>
       </c>
       <c r="P60">
-        <v>6.964317549000002</v>
+        <v>6.906191989500003</v>
       </c>
       <c r="Q60">
-        <v>9.504317549000003</v>
+        <v>9.446191989500003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09407984372549461</v>
+        <v>0.09515179394225065</v>
       </c>
       <c r="T60">
-        <v>0.9410640174357597</v>
+        <v>0.9619583223802243</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.065776941037446</v>
+        <v>3.013814620002913</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06964562551632278</v>
+        <v>0.0734543366679378</v>
       </c>
       <c r="C61">
-        <v>43.12122225155439</v>
+        <v>33.45679607166471</v>
       </c>
       <c r="D61">
-        <v>87.07172225155438</v>
+        <v>78.52679607166471</v>
       </c>
       <c r="E61">
-        <v>65.20049999999999</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F61">
-        <v>66.05049999999999</v>
+        <v>67.16999999999999</v>
       </c>
       <c r="G61">
         <v>22.1</v>
@@ -6289,45 +6289,45 @@
         <v>12.76</v>
       </c>
       <c r="M61">
-        <v>4.233837049999999</v>
+        <v>4.829522999999999</v>
       </c>
       <c r="N61">
-        <v>8.526162950000003</v>
+        <v>7.930477000000002</v>
       </c>
       <c r="O61">
-        <v>1.619970960500001</v>
+        <v>1.50679063</v>
       </c>
       <c r="P61">
-        <v>6.906191989500003</v>
+        <v>6.423686370000002</v>
       </c>
       <c r="Q61">
-        <v>9.446191989500003</v>
+        <v>8.963686370000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09515179394225065</v>
+        <v>0.0962773416698445</v>
       </c>
       <c r="T61">
-        <v>0.9619583223802243</v>
+        <v>0.983897342571912</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.19</v>
       </c>
       <c r="W61">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.013814620002913</v>
+        <v>2.642082872366485</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0734543366679378</v>
+        <v>0.07353542781955283</v>
       </c>
       <c r="C62">
-        <v>33.45679607166471</v>
+        <v>32.17356239626933</v>
       </c>
       <c r="D62">
-        <v>78.52679607166471</v>
+        <v>78.36306239626931</v>
       </c>
       <c r="E62">
-        <v>66.31999999999999</v>
+        <v>67.4395</v>
       </c>
       <c r="F62">
-        <v>67.16999999999999</v>
+        <v>68.28949999999999</v>
       </c>
       <c r="G62">
         <v>22.1</v>
@@ -6371,28 +6371,28 @@
         <v>12.76</v>
       </c>
       <c r="M62">
-        <v>4.829522999999999</v>
+        <v>4.910015049999999</v>
       </c>
       <c r="N62">
-        <v>7.930477000000002</v>
+        <v>7.849984950000002</v>
       </c>
       <c r="O62">
-        <v>1.50679063</v>
+        <v>1.4914971405</v>
       </c>
       <c r="P62">
-        <v>6.423686370000002</v>
+        <v>6.358487809500001</v>
       </c>
       <c r="Q62">
-        <v>8.963686370000001</v>
+        <v>8.898487809500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.0962773416698445</v>
+        <v>0.09746060979372521</v>
       </c>
       <c r="T62">
-        <v>0.983897342571912</v>
+        <v>1.006961440722148</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.642082872366485</v>
+        <v>2.598770038393264</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07353542781955283</v>
+        <v>0.07361651897116786</v>
       </c>
       <c r="C63">
-        <v>32.17356239626933</v>
+        <v>30.89101009172106</v>
       </c>
       <c r="D63">
-        <v>78.36306239626931</v>
+        <v>78.20001009172105</v>
       </c>
       <c r="E63">
-        <v>67.4395</v>
+        <v>68.559</v>
       </c>
       <c r="F63">
-        <v>68.28949999999999</v>
+        <v>69.40899999999999</v>
       </c>
       <c r="G63">
         <v>22.1</v>
@@ -6453,28 +6453,28 @@
         <v>12.76</v>
       </c>
       <c r="M63">
-        <v>4.910015049999999</v>
+        <v>4.990507099999999</v>
       </c>
       <c r="N63">
-        <v>7.849984950000002</v>
+        <v>7.769492900000002</v>
       </c>
       <c r="O63">
-        <v>1.4914971405</v>
+        <v>1.476203651000001</v>
       </c>
       <c r="P63">
-        <v>6.358487809500001</v>
+        <v>6.293289249000002</v>
       </c>
       <c r="Q63">
-        <v>8.898487809500001</v>
+        <v>8.833289249000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09746060979372521</v>
+        <v>0.09870615518728386</v>
       </c>
       <c r="T63">
-        <v>1.006961440722148</v>
+        <v>1.031239438775028</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.598770038393264</v>
+        <v>2.556854392612727</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07361651897116786</v>
+        <v>0.07369761012278289</v>
       </c>
       <c r="C64">
-        <v>30.89101009172106</v>
+        <v>29.60913491360698</v>
       </c>
       <c r="D64">
-        <v>78.20001009172105</v>
+        <v>78.03763491360698</v>
       </c>
       <c r="E64">
-        <v>68.559</v>
+        <v>69.6785</v>
       </c>
       <c r="F64">
-        <v>69.40899999999999</v>
+        <v>70.52849999999999</v>
       </c>
       <c r="G64">
         <v>22.1</v>
@@ -6535,28 +6535,28 @@
         <v>12.76</v>
       </c>
       <c r="M64">
-        <v>4.990507099999999</v>
+        <v>5.07099915</v>
       </c>
       <c r="N64">
-        <v>7.769492900000002</v>
+        <v>7.689000850000002</v>
       </c>
       <c r="O64">
-        <v>1.476203651000001</v>
+        <v>1.4609101615</v>
       </c>
       <c r="P64">
-        <v>6.293289249000002</v>
+        <v>6.228090688500002</v>
       </c>
       <c r="Q64">
-        <v>8.833289249000002</v>
+        <v>8.768090688500003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09870615518728386</v>
+        <v>0.1000190273588727</v>
       </c>
       <c r="T64">
-        <v>1.031239438775028</v>
+        <v>1.056829761046982</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.556854392612727</v>
+        <v>2.516269402253795</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07369761012278289</v>
+        <v>0.07580046127439793</v>
       </c>
       <c r="C65">
-        <v>29.60913491360698</v>
+        <v>24.502369671943</v>
       </c>
       <c r="D65">
-        <v>78.03763491360698</v>
+        <v>74.050369671943</v>
       </c>
       <c r="E65">
-        <v>69.6785</v>
+        <v>70.798</v>
       </c>
       <c r="F65">
-        <v>70.52849999999999</v>
+        <v>71.648</v>
       </c>
       <c r="G65">
         <v>22.1</v>
@@ -6617,45 +6617,45 @@
         <v>12.76</v>
       </c>
       <c r="M65">
-        <v>5.07099915</v>
+        <v>5.4309184</v>
       </c>
       <c r="N65">
-        <v>7.689000850000002</v>
+        <v>7.329081600000001</v>
       </c>
       <c r="O65">
-        <v>1.4609101615</v>
+        <v>1.392525504</v>
       </c>
       <c r="P65">
-        <v>6.228090688500002</v>
+        <v>5.936556096000001</v>
       </c>
       <c r="Q65">
-        <v>8.768090688500003</v>
+        <v>8.476556096000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1000190273588727</v>
+        <v>0.1014048368733276</v>
       </c>
       <c r="T65">
-        <v>1.056829761046982</v>
+        <v>1.083841767889601</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.516269402253795</v>
+        <v>2.349510535823923</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07580046127439793</v>
+        <v>0.07591314242601296</v>
       </c>
       <c r="C66">
-        <v>24.502369671943</v>
+        <v>23.18068250656218</v>
       </c>
       <c r="D66">
-        <v>74.050369671943</v>
+        <v>73.84818250656217</v>
       </c>
       <c r="E66">
-        <v>70.798</v>
+        <v>71.9175</v>
       </c>
       <c r="F66">
-        <v>71.648</v>
+        <v>72.7675</v>
       </c>
       <c r="G66">
         <v>22.1</v>
@@ -6699,28 +6699,28 @@
         <v>12.76</v>
       </c>
       <c r="M66">
-        <v>5.4309184</v>
+        <v>5.5157765</v>
       </c>
       <c r="N66">
-        <v>7.329081600000001</v>
+        <v>7.244223500000001</v>
       </c>
       <c r="O66">
-        <v>1.392525504</v>
+        <v>1.376402465</v>
       </c>
       <c r="P66">
-        <v>5.936556096000001</v>
+        <v>5.867821035000001</v>
       </c>
       <c r="Q66">
-        <v>8.476556096000001</v>
+        <v>8.407821035000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1014048368733276</v>
+        <v>0.1028698355028942</v>
       </c>
       <c r="T66">
-        <v>1.083841767889601</v>
+        <v>1.112397317980369</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.349510535823923</v>
+        <v>2.31336421988817</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07591314242601296</v>
+        <v>0.07602582357762799</v>
       </c>
       <c r="C67">
-        <v>23.18068250656218</v>
+        <v>21.86009643861382</v>
       </c>
       <c r="D67">
-        <v>73.84818250656217</v>
+        <v>73.64709643861383</v>
       </c>
       <c r="E67">
-        <v>71.9175</v>
+        <v>73.03700000000001</v>
       </c>
       <c r="F67">
-        <v>72.7675</v>
+        <v>73.887</v>
       </c>
       <c r="G67">
         <v>22.1</v>
@@ -6781,28 +6781,28 @@
         <v>12.76</v>
       </c>
       <c r="M67">
-        <v>5.5157765</v>
+        <v>5.6006346</v>
       </c>
       <c r="N67">
-        <v>7.244223500000001</v>
+        <v>7.159365400000001</v>
       </c>
       <c r="O67">
-        <v>1.376402465</v>
+        <v>1.360279426</v>
       </c>
       <c r="P67">
-        <v>5.867821035000001</v>
+        <v>5.799085974000001</v>
       </c>
       <c r="Q67">
-        <v>8.407821035000001</v>
+        <v>8.339085974000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1028698355028942</v>
+        <v>0.1044210105224353</v>
       </c>
       <c r="T67">
-        <v>1.112397317980369</v>
+        <v>1.142632606311771</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.31336421988817</v>
+        <v>2.278313246859561</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07602582357762799</v>
+        <v>0.07613850472924302</v>
       </c>
       <c r="C68">
-        <v>21.86009643861382</v>
+        <v>20.54060249777221</v>
       </c>
       <c r="D68">
-        <v>73.64709643861383</v>
+        <v>73.44710249777222</v>
       </c>
       <c r="E68">
-        <v>73.03700000000001</v>
+        <v>74.15650000000001</v>
       </c>
       <c r="F68">
-        <v>73.887</v>
+        <v>75.0065</v>
       </c>
       <c r="G68">
         <v>22.1</v>
@@ -6863,28 +6863,28 @@
         <v>12.76</v>
       </c>
       <c r="M68">
-        <v>5.6006346</v>
+        <v>5.685492700000001</v>
       </c>
       <c r="N68">
-        <v>7.159365400000001</v>
+        <v>7.0745073</v>
       </c>
       <c r="O68">
-        <v>1.360279426</v>
+        <v>1.344156387</v>
       </c>
       <c r="P68">
-        <v>5.799085974000001</v>
+        <v>5.730350913000001</v>
       </c>
       <c r="Q68">
-        <v>8.339085974000001</v>
+        <v>8.270350913000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1044210105224353</v>
+        <v>0.1060661961492213</v>
       </c>
       <c r="T68">
-        <v>1.142632606311771</v>
+        <v>1.174700336360227</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.278313246859561</v>
+        <v>2.244308571533299</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07613850472924302</v>
+        <v>0.07625118588085805</v>
       </c>
       <c r="C69">
-        <v>20.54060249777221</v>
+        <v>19.22219181088602</v>
       </c>
       <c r="D69">
-        <v>73.44710249777222</v>
+        <v>73.24819181088601</v>
       </c>
       <c r="E69">
-        <v>74.15650000000001</v>
+        <v>75.27600000000001</v>
       </c>
       <c r="F69">
-        <v>75.0065</v>
+        <v>76.126</v>
       </c>
       <c r="G69">
         <v>22.1</v>
@@ -6945,28 +6945,28 @@
         <v>12.76</v>
       </c>
       <c r="M69">
-        <v>5.685492700000001</v>
+        <v>5.770350800000001</v>
       </c>
       <c r="N69">
-        <v>7.0745073</v>
+        <v>6.989649200000001</v>
       </c>
       <c r="O69">
-        <v>1.344156387</v>
+        <v>1.328033348</v>
       </c>
       <c r="P69">
-        <v>5.730350913000001</v>
+        <v>5.661615852000001</v>
       </c>
       <c r="Q69">
-        <v>8.270350913000001</v>
+        <v>8.201615852</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1060661961492213</v>
+        <v>0.1078142058776814</v>
       </c>
       <c r="T69">
-        <v>1.174700336360227</v>
+        <v>1.208772299536712</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.244308571533299</v>
+        <v>2.211304033716633</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07625118588085805</v>
+        <v>0.07636386703247311</v>
       </c>
       <c r="C70">
-        <v>19.22219181088602</v>
+        <v>17.90485560066583</v>
       </c>
       <c r="D70">
-        <v>73.24819181088601</v>
+        <v>73.05035560066581</v>
       </c>
       <c r="E70">
-        <v>75.27600000000001</v>
+        <v>76.3955</v>
       </c>
       <c r="F70">
-        <v>76.126</v>
+        <v>77.24549999999999</v>
       </c>
       <c r="G70">
         <v>22.1</v>
@@ -7027,28 +7027,28 @@
         <v>12.76</v>
       </c>
       <c r="M70">
-        <v>5.770350800000001</v>
+        <v>5.8552089</v>
       </c>
       <c r="N70">
-        <v>6.989649200000001</v>
+        <v>6.904791100000002</v>
       </c>
       <c r="O70">
-        <v>1.328033348</v>
+        <v>1.311910309</v>
       </c>
       <c r="P70">
-        <v>5.661615852000001</v>
+        <v>5.592880791000001</v>
       </c>
       <c r="Q70">
-        <v>8.201615852</v>
+        <v>8.132880791000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1078142058776814</v>
+        <v>0.1096749904273326</v>
       </c>
       <c r="T70">
-        <v>1.208772299536712</v>
+        <v>1.245042453885873</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.211304033716633</v>
+        <v>2.179256149170016</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07636386703247311</v>
+        <v>0.07647654818408814</v>
       </c>
       <c r="C71">
-        <v>17.90485560066583</v>
+        <v>16.58858518439338</v>
       </c>
       <c r="D71">
-        <v>73.05035560066581</v>
+        <v>72.85358518439338</v>
       </c>
       <c r="E71">
-        <v>76.3955</v>
+        <v>77.515</v>
       </c>
       <c r="F71">
-        <v>77.24549999999999</v>
+        <v>78.36499999999999</v>
       </c>
       <c r="G71">
         <v>22.1</v>
@@ -7109,28 +7109,28 @@
         <v>12.76</v>
       </c>
       <c r="M71">
-        <v>5.8552089</v>
+        <v>5.940067</v>
       </c>
       <c r="N71">
-        <v>6.904791100000002</v>
+        <v>6.819933000000002</v>
       </c>
       <c r="O71">
-        <v>1.311910309</v>
+        <v>1.29578727</v>
       </c>
       <c r="P71">
-        <v>5.592880791000001</v>
+        <v>5.524145730000001</v>
       </c>
       <c r="Q71">
-        <v>8.132880791000002</v>
+        <v>8.06414573</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1096749904273326</v>
+        <v>0.1116598272802937</v>
       </c>
       <c r="T71">
-        <v>1.245042453885873</v>
+        <v>1.283730618524978</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.179256149170016</v>
+        <v>2.148123918467586</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07647654818408814</v>
+        <v>0.07658922933570317</v>
       </c>
       <c r="C72">
-        <v>16.58858518439338</v>
+        <v>15.27337197265101</v>
       </c>
       <c r="D72">
-        <v>72.85358518439338</v>
+        <v>72.65787197265101</v>
       </c>
       <c r="E72">
-        <v>77.515</v>
+        <v>78.6345</v>
       </c>
       <c r="F72">
-        <v>78.36499999999999</v>
+        <v>79.4845</v>
       </c>
       <c r="G72">
         <v>22.1</v>
@@ -7191,28 +7191,28 @@
         <v>12.76</v>
       </c>
       <c r="M72">
-        <v>5.940067</v>
+        <v>6.0249251</v>
       </c>
       <c r="N72">
-        <v>6.819933000000002</v>
+        <v>6.735074900000002</v>
       </c>
       <c r="O72">
-        <v>1.29578727</v>
+        <v>1.279664231</v>
       </c>
       <c r="P72">
-        <v>5.524145730000001</v>
+        <v>5.455410669000001</v>
       </c>
       <c r="Q72">
-        <v>8.06414573</v>
+        <v>7.995410669000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1116598272802937</v>
+        <v>0.1137815494334592</v>
       </c>
       <c r="T72">
-        <v>1.283730618524978</v>
+        <v>1.325086932449539</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.148123918467586</v>
+        <v>2.117868652010297</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07658922933570317</v>
+        <v>0.0767019104873182</v>
       </c>
       <c r="C73">
-        <v>15.27337197265102</v>
+        <v>13.95920746807195</v>
       </c>
       <c r="D73">
-        <v>72.65787197265101</v>
+        <v>72.46320746807194</v>
       </c>
       <c r="E73">
-        <v>78.63449999999999</v>
+        <v>79.75399999999999</v>
       </c>
       <c r="F73">
-        <v>79.48449999999998</v>
+        <v>80.60399999999998</v>
       </c>
       <c r="G73">
         <v>22.1</v>
@@ -7273,28 +7273,28 @@
         <v>12.76</v>
       </c>
       <c r="M73">
-        <v>6.024925099999999</v>
+        <v>6.109783199999999</v>
       </c>
       <c r="N73">
-        <v>6.735074900000003</v>
+        <v>6.650216800000003</v>
       </c>
       <c r="O73">
-        <v>1.279664231000001</v>
+        <v>1.263541192000001</v>
       </c>
       <c r="P73">
-        <v>5.455410669000002</v>
+        <v>5.386675608000002</v>
       </c>
       <c r="Q73">
-        <v>7.995410669000002</v>
+        <v>7.926675608000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1137815494334591</v>
+        <v>0.1160548231689935</v>
       </c>
       <c r="T73">
-        <v>1.325086932449539</v>
+        <v>1.369397268797282</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.117868652010297</v>
+        <v>2.088453809621265</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0767019104873182</v>
+        <v>0.07681459163893323</v>
       </c>
       <c r="C74">
-        <v>13.95920746807195</v>
+        <v>12.6460832641104</v>
       </c>
       <c r="D74">
-        <v>72.46320746807194</v>
+        <v>72.26958326411038</v>
       </c>
       <c r="E74">
-        <v>79.75399999999999</v>
+        <v>80.87349999999999</v>
       </c>
       <c r="F74">
-        <v>80.60399999999998</v>
+        <v>81.72349999999999</v>
       </c>
       <c r="G74">
         <v>22.1</v>
@@ -7355,28 +7355,28 @@
         <v>12.76</v>
       </c>
       <c r="M74">
-        <v>6.109783199999999</v>
+        <v>6.1946413</v>
       </c>
       <c r="N74">
-        <v>6.650216800000003</v>
+        <v>6.565358700000002</v>
       </c>
       <c r="O74">
-        <v>1.263541192000001</v>
+        <v>1.247418153</v>
       </c>
       <c r="P74">
-        <v>5.386675608000002</v>
+        <v>5.317940547000001</v>
       </c>
       <c r="Q74">
-        <v>7.926675608000002</v>
+        <v>7.857940547000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1160548231689935</v>
+        <v>0.1184964875516045</v>
       </c>
       <c r="T74">
-        <v>1.369397268797282</v>
+        <v>1.416989852281896</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.088453809621265</v>
+        <v>2.059844853325083</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07681459163893323</v>
+        <v>0.07692727279054826</v>
       </c>
       <c r="C75">
-        <v>12.6460832641104</v>
+        <v>11.3339910438315</v>
       </c>
       <c r="D75">
-        <v>72.26958326411038</v>
+        <v>72.0769910438315</v>
       </c>
       <c r="E75">
-        <v>80.87349999999999</v>
+        <v>81.99299999999999</v>
       </c>
       <c r="F75">
-        <v>81.72349999999999</v>
+        <v>82.84299999999999</v>
       </c>
       <c r="G75">
         <v>22.1</v>
@@ -7437,28 +7437,28 @@
         <v>12.76</v>
       </c>
       <c r="M75">
-        <v>6.1946413</v>
+        <v>6.2794994</v>
       </c>
       <c r="N75">
-        <v>6.565358700000002</v>
+        <v>6.480500600000002</v>
       </c>
       <c r="O75">
-        <v>1.247418153</v>
+        <v>1.231295114</v>
       </c>
       <c r="P75">
-        <v>5.317940547000001</v>
+        <v>5.249205486000001</v>
       </c>
       <c r="Q75">
-        <v>7.857940547000001</v>
+        <v>7.789205486000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1184964875516045</v>
+        <v>0.1211259722713394</v>
       </c>
       <c r="T75">
-        <v>1.416989852281896</v>
+        <v>1.468243403726864</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.059844853325083</v>
+        <v>2.032009112063934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07692727279054826</v>
+        <v>0.07703995394216329</v>
       </c>
       <c r="C76">
-        <v>11.3339910438315</v>
+        <v>10.02292257872047</v>
       </c>
       <c r="D76">
-        <v>72.0769910438315</v>
+        <v>71.88542257872045</v>
       </c>
       <c r="E76">
-        <v>81.99299999999999</v>
+        <v>83.1125</v>
       </c>
       <c r="F76">
-        <v>82.84299999999999</v>
+        <v>83.96249999999999</v>
       </c>
       <c r="G76">
         <v>22.1</v>
@@ -7519,28 +7519,28 @@
         <v>12.76</v>
       </c>
       <c r="M76">
-        <v>6.2794994</v>
+        <v>6.3643575</v>
       </c>
       <c r="N76">
-        <v>6.480500600000002</v>
+        <v>6.395642500000002</v>
       </c>
       <c r="O76">
-        <v>1.231295114</v>
+        <v>1.215172075</v>
       </c>
       <c r="P76">
-        <v>5.249205486000001</v>
+        <v>5.180470425000001</v>
       </c>
       <c r="Q76">
-        <v>7.789205486000001</v>
+        <v>7.720470425000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1211259722713394</v>
+        <v>0.1239658157686531</v>
       </c>
       <c r="T76">
-        <v>1.468243403726864</v>
+        <v>1.52359723928743</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.032009112063934</v>
+        <v>2.004915657236414</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07703995394216329</v>
+        <v>0.08589415509377832</v>
       </c>
       <c r="C77">
-        <v>10.02292257872047</v>
+        <v>-3.515829694969028</v>
       </c>
       <c r="D77">
-        <v>71.88542257872045</v>
+        <v>59.46617030503096</v>
       </c>
       <c r="E77">
-        <v>83.1125</v>
+        <v>84.232</v>
       </c>
       <c r="F77">
-        <v>83.96249999999999</v>
+        <v>85.08199999999999</v>
       </c>
       <c r="G77">
         <v>22.1</v>
@@ -7601,45 +7601,45 @@
         <v>12.76</v>
       </c>
       <c r="M77">
-        <v>6.3643575</v>
+        <v>7.657379999999999</v>
       </c>
       <c r="N77">
-        <v>6.395642500000002</v>
+        <v>5.102620000000003</v>
       </c>
       <c r="O77">
-        <v>1.215172075</v>
+        <v>0.9694978000000005</v>
       </c>
       <c r="P77">
-        <v>5.180470425000001</v>
+        <v>4.133122200000003</v>
       </c>
       <c r="Q77">
-        <v>7.720470425000001</v>
+        <v>6.673122200000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1239658157686531</v>
+        <v>0.127042312890743</v>
       </c>
       <c r="T77">
-        <v>1.52359723928743</v>
+        <v>1.583563894478044</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.19</v>
       </c>
       <c r="W77">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.004915657236414</v>
+        <v>1.666366302834652</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08589415509377832</v>
+        <v>0.08612185624539336</v>
       </c>
       <c r="C78">
-        <v>-3.515829694969028</v>
+        <v>-4.898365676809945</v>
       </c>
       <c r="D78">
-        <v>59.46617030503096</v>
+        <v>59.20313432319005</v>
       </c>
       <c r="E78">
-        <v>84.232</v>
+        <v>85.3515</v>
       </c>
       <c r="F78">
-        <v>85.08199999999999</v>
+        <v>86.2015</v>
       </c>
       <c r="G78">
         <v>22.1</v>
@@ -7683,28 +7683,28 @@
         <v>12.76</v>
       </c>
       <c r="M78">
-        <v>7.657379999999999</v>
+        <v>7.758134999999999</v>
       </c>
       <c r="N78">
-        <v>5.102620000000003</v>
+        <v>5.001865000000002</v>
       </c>
       <c r="O78">
-        <v>0.9694978000000005</v>
+        <v>0.9503543500000005</v>
       </c>
       <c r="P78">
-        <v>4.133122200000003</v>
+        <v>4.051510650000002</v>
       </c>
       <c r="Q78">
-        <v>6.673122200000003</v>
+        <v>6.591510650000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.127042312890743</v>
+        <v>0.1303863315017102</v>
       </c>
       <c r="T78">
-        <v>1.583563894478044</v>
+        <v>1.648745041424363</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.666366302834652</v>
+        <v>1.644725182018617</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08612185624539336</v>
+        <v>0.08634955739700839</v>
       </c>
       <c r="C79">
-        <v>-4.898365676809945</v>
+        <v>-6.278584938505247</v>
       </c>
       <c r="D79">
-        <v>59.20313432319005</v>
+        <v>58.94241506149475</v>
       </c>
       <c r="E79">
-        <v>85.3515</v>
+        <v>86.471</v>
       </c>
       <c r="F79">
-        <v>86.2015</v>
+        <v>87.321</v>
       </c>
       <c r="G79">
         <v>22.1</v>
@@ -7765,28 +7765,28 @@
         <v>12.76</v>
       </c>
       <c r="M79">
-        <v>7.758134999999999</v>
+        <v>7.85889</v>
       </c>
       <c r="N79">
-        <v>5.001865000000002</v>
+        <v>4.901110000000002</v>
       </c>
       <c r="O79">
-        <v>0.9503543500000005</v>
+        <v>0.9312109000000004</v>
       </c>
       <c r="P79">
-        <v>4.051510650000002</v>
+        <v>3.969899100000001</v>
       </c>
       <c r="Q79">
-        <v>6.591510650000002</v>
+        <v>6.509899100000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1303863315017102</v>
+        <v>0.1340343518045835</v>
       </c>
       <c r="T79">
-        <v>1.648745041424363</v>
+        <v>1.719851747183983</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.644725182018617</v>
+        <v>1.623638961736327</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08634955739700839</v>
+        <v>0.08657725854862341</v>
       </c>
       <c r="C80">
-        <v>-6.278584938505247</v>
+        <v>-7.656517953032861</v>
       </c>
       <c r="D80">
-        <v>58.94241506149475</v>
+        <v>58.68398204696715</v>
       </c>
       <c r="E80">
-        <v>86.471</v>
+        <v>87.59050000000001</v>
       </c>
       <c r="F80">
-        <v>87.321</v>
+        <v>88.4405</v>
       </c>
       <c r="G80">
         <v>22.1</v>
@@ -7847,28 +7847,28 @@
         <v>12.76</v>
       </c>
       <c r="M80">
-        <v>7.85889</v>
+        <v>7.959645</v>
       </c>
       <c r="N80">
-        <v>4.901110000000002</v>
+        <v>4.800355000000001</v>
       </c>
       <c r="O80">
-        <v>0.9312109000000004</v>
+        <v>0.9120674500000003</v>
       </c>
       <c r="P80">
-        <v>3.969899100000001</v>
+        <v>3.888287550000001</v>
       </c>
       <c r="Q80">
-        <v>6.509899100000002</v>
+        <v>6.428287550000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1340343518045835</v>
+        <v>0.1380298026124924</v>
       </c>
       <c r="T80">
-        <v>1.719851747183983</v>
+        <v>1.797730520158805</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.623638961736327</v>
+        <v>1.603086569815614</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08657725854862341</v>
+        <v>0.08680495970023845</v>
       </c>
       <c r="C81">
-        <v>-7.656517953032861</v>
+        <v>-9.032194661268647</v>
       </c>
       <c r="D81">
-        <v>58.68398204696715</v>
+        <v>58.42780533873136</v>
       </c>
       <c r="E81">
-        <v>87.59050000000001</v>
+        <v>88.71000000000001</v>
       </c>
       <c r="F81">
-        <v>88.4405</v>
+        <v>89.56</v>
       </c>
       <c r="G81">
         <v>22.1</v>
@@ -7929,28 +7929,28 @@
         <v>12.76</v>
       </c>
       <c r="M81">
-        <v>7.959645</v>
+        <v>8.0604</v>
       </c>
       <c r="N81">
-        <v>4.800355000000001</v>
+        <v>4.699600000000002</v>
       </c>
       <c r="O81">
-        <v>0.9120674500000003</v>
+        <v>0.8929240000000004</v>
       </c>
       <c r="P81">
-        <v>3.888287550000001</v>
+        <v>3.806676000000002</v>
       </c>
       <c r="Q81">
-        <v>6.428287550000001</v>
+        <v>6.346676000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1380298026124924</v>
+        <v>0.1424247985011922</v>
       </c>
       <c r="T81">
-        <v>1.797730520158805</v>
+        <v>1.88339717043111</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.603086569815614</v>
+        <v>1.583047987692919</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08680495970023845</v>
+        <v>0.08703266085185349</v>
       </c>
       <c r="C82">
-        <v>-9.032194661268647</v>
+        <v>-10.40564448354996</v>
       </c>
       <c r="D82">
-        <v>58.42780533873136</v>
+        <v>58.17385551645002</v>
       </c>
       <c r="E82">
-        <v>88.71000000000001</v>
+        <v>89.8295</v>
       </c>
       <c r="F82">
-        <v>89.56</v>
+        <v>90.67949999999999</v>
       </c>
       <c r="G82">
         <v>22.1</v>
@@ -8011,28 +8011,28 @@
         <v>12.76</v>
       </c>
       <c r="M82">
-        <v>8.0604</v>
+        <v>8.161154999999999</v>
       </c>
       <c r="N82">
-        <v>4.699600000000002</v>
+        <v>4.598845000000003</v>
       </c>
       <c r="O82">
-        <v>0.8929240000000004</v>
+        <v>0.8737805500000004</v>
       </c>
       <c r="P82">
-        <v>3.806676000000002</v>
+        <v>3.725064450000002</v>
       </c>
       <c r="Q82">
-        <v>6.346676000000002</v>
+        <v>6.265064450000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1424247985011922</v>
+        <v>0.1472824255360709</v>
       </c>
       <c r="T82">
-        <v>1.88339717043111</v>
+        <v>1.978081362837341</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.583047987692919</v>
+        <v>1.563504185375722</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08703266085185349</v>
+        <v>0.08726036200346851</v>
       </c>
       <c r="C83">
-        <v>-10.40564448354996</v>
+        <v>-11.7768963309391</v>
       </c>
       <c r="D83">
-        <v>58.17385551645002</v>
+        <v>57.92210366906089</v>
       </c>
       <c r="E83">
-        <v>89.8295</v>
+        <v>90.949</v>
       </c>
       <c r="F83">
-        <v>90.67949999999999</v>
+        <v>91.79899999999999</v>
       </c>
       <c r="G83">
         <v>22.1</v>
@@ -8093,28 +8093,28 @@
         <v>12.76</v>
       </c>
       <c r="M83">
-        <v>8.161154999999999</v>
+        <v>8.261909999999999</v>
       </c>
       <c r="N83">
-        <v>4.598845000000003</v>
+        <v>4.498090000000003</v>
       </c>
       <c r="O83">
-        <v>0.8737805500000004</v>
+        <v>0.8546371000000006</v>
       </c>
       <c r="P83">
-        <v>3.725064450000002</v>
+        <v>3.643452900000002</v>
       </c>
       <c r="Q83">
-        <v>6.265064450000002</v>
+        <v>6.183452900000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1472824255360709</v>
+        <v>0.1526797889081584</v>
       </c>
       <c r="T83">
-        <v>1.978081362837341</v>
+        <v>2.083286021066487</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.563504185375722</v>
+        <v>1.544437061163823</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08726036200346851</v>
+        <v>0.08748806315508355</v>
       </c>
       <c r="C84">
-        <v>-11.7768963309391</v>
+        <v>-13.14597861619535</v>
       </c>
       <c r="D84">
-        <v>57.92210366906089</v>
+        <v>57.67252138380464</v>
       </c>
       <c r="E84">
-        <v>90.949</v>
+        <v>92.0685</v>
       </c>
       <c r="F84">
-        <v>91.79899999999999</v>
+        <v>92.91849999999999</v>
       </c>
       <c r="G84">
         <v>22.1</v>
@@ -8175,28 +8175,28 @@
         <v>12.76</v>
       </c>
       <c r="M84">
-        <v>8.261909999999999</v>
+        <v>8.362665</v>
       </c>
       <c r="N84">
-        <v>4.498090000000003</v>
+        <v>4.397335000000002</v>
       </c>
       <c r="O84">
-        <v>0.8546371000000006</v>
+        <v>0.8354936500000003</v>
       </c>
       <c r="P84">
-        <v>3.643452900000002</v>
+        <v>3.561841350000002</v>
       </c>
       <c r="Q84">
-        <v>6.183452900000002</v>
+        <v>6.101841350000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1526797889081584</v>
+        <v>0.1587121362063738</v>
       </c>
       <c r="T84">
-        <v>2.083286021066487</v>
+        <v>2.200867697910827</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.544437061163823</v>
+        <v>1.525829385728114</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08748806315508355</v>
+        <v>0.08771576430669858</v>
       </c>
       <c r="C85">
-        <v>-13.14597861619535</v>
+        <v>-14.51291926446477</v>
       </c>
       <c r="D85">
-        <v>57.67252138380464</v>
+        <v>57.42508073553523</v>
       </c>
       <c r="E85">
-        <v>92.0685</v>
+        <v>93.188</v>
       </c>
       <c r="F85">
-        <v>92.91849999999999</v>
+        <v>94.038</v>
       </c>
       <c r="G85">
         <v>22.1</v>
@@ -8257,28 +8257,28 @@
         <v>12.76</v>
       </c>
       <c r="M85">
-        <v>8.362665</v>
+        <v>8.463419999999999</v>
       </c>
       <c r="N85">
-        <v>4.397335000000002</v>
+        <v>4.296580000000002</v>
       </c>
       <c r="O85">
-        <v>0.8354936500000003</v>
+        <v>0.8163502000000005</v>
       </c>
       <c r="P85">
-        <v>3.561841350000002</v>
+        <v>3.480229800000002</v>
       </c>
       <c r="Q85">
-        <v>6.101841350000002</v>
+        <v>6.020229800000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1587121362063738</v>
+        <v>0.1654985269168661</v>
       </c>
       <c r="T85">
-        <v>2.200867697910827</v>
+        <v>2.333147084360709</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.525829385728114</v>
+        <v>1.507664750183732</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08771576430669857</v>
+        <v>0.1294209324440987</v>
       </c>
       <c r="C86">
-        <v>-14.51291926446473</v>
+        <v>-40.90147824841183</v>
       </c>
       <c r="D86">
-        <v>57.42508073553525</v>
+        <v>32.15602175158815</v>
       </c>
       <c r="E86">
-        <v>93.18799999999999</v>
+        <v>94.30749999999999</v>
       </c>
       <c r="F86">
-        <v>94.03799999999998</v>
+        <v>95.15749999999998</v>
       </c>
       <c r="G86">
         <v>22.1</v>
@@ -8339,45 +8339,45 @@
         <v>12.76</v>
       </c>
       <c r="M86">
-        <v>8.463419999999998</v>
+        <v>13.969121</v>
       </c>
       <c r="N86">
-        <v>4.296580000000004</v>
+        <v>-1.209120999999998</v>
       </c>
       <c r="O86">
-        <v>0.8163502000000008</v>
+        <v>-0.2297329899999996</v>
       </c>
       <c r="P86">
-        <v>3.480229800000003</v>
+        <v>-0.9793880099999983</v>
       </c>
       <c r="Q86">
-        <v>6.020229800000003</v>
+        <v>1.560611990000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.165498526916866</v>
+        <v>0.1753135261049186</v>
       </c>
       <c r="T86">
-        <v>2.333147084360708</v>
+        <v>2.524459687184234</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.19</v>
+        <v>0.1735542272130079</v>
       </c>
       <c r="W86">
-        <v>0.07290000000000001</v>
+        <v>0.1213222394451304</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.507664750183733</v>
+        <v>0.9134433011210943</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1294209324440987</v>
+        <v>0.1304309324440987</v>
       </c>
       <c r="C87">
-        <v>-40.90147824841183</v>
+        <v>-42.36003909833939</v>
       </c>
       <c r="D87">
-        <v>32.15602175158815</v>
+        <v>31.8169609016606</v>
       </c>
       <c r="E87">
-        <v>94.30749999999999</v>
+        <v>95.42699999999999</v>
       </c>
       <c r="F87">
-        <v>95.15749999999998</v>
+        <v>96.27699999999999</v>
       </c>
       <c r="G87">
         <v>22.1</v>
@@ -8421,37 +8421,37 @@
         <v>12.76</v>
       </c>
       <c r="M87">
-        <v>13.969121</v>
+        <v>14.1334636</v>
       </c>
       <c r="N87">
-        <v>-1.209120999999998</v>
+        <v>-1.373463599999997</v>
       </c>
       <c r="O87">
-        <v>-0.2297329899999996</v>
+        <v>-0.2609580839999995</v>
       </c>
       <c r="P87">
-        <v>-0.9793880099999983</v>
+        <v>-1.112505515999998</v>
       </c>
       <c r="Q87">
-        <v>1.560611990000002</v>
+        <v>1.427494484000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1753135261049186</v>
+        <v>0.1845644922552699</v>
       </c>
       <c r="T87">
-        <v>2.524459687184234</v>
+        <v>2.704778236268822</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1735542272130079</v>
+        <v>0.1715361548035543</v>
       </c>
       <c r="W87">
-        <v>0.1213222394451304</v>
+        <v>0.1216184924748382</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9134433011210943</v>
+        <v>0.9028218673871281</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1304309324440987</v>
+        <v>0.1314409324440987</v>
       </c>
       <c r="C88">
-        <v>-42.36003909833939</v>
+        <v>-43.81152427707302</v>
       </c>
       <c r="D88">
-        <v>31.8169609016606</v>
+        <v>31.48497572292697</v>
       </c>
       <c r="E88">
-        <v>95.42699999999999</v>
+        <v>96.54649999999999</v>
       </c>
       <c r="F88">
-        <v>96.27699999999999</v>
+        <v>97.39649999999999</v>
       </c>
       <c r="G88">
         <v>22.1</v>
@@ -8503,37 +8503,37 @@
         <v>12.76</v>
       </c>
       <c r="M88">
-        <v>14.1334636</v>
+        <v>14.2978062</v>
       </c>
       <c r="N88">
-        <v>-1.373463599999997</v>
+        <v>-1.537806199999999</v>
       </c>
       <c r="O88">
-        <v>-0.2609580839999995</v>
+        <v>-0.2921831779999997</v>
       </c>
       <c r="P88">
-        <v>-1.112505515999998</v>
+        <v>-1.245623021999999</v>
       </c>
       <c r="Q88">
-        <v>1.427494484000002</v>
+        <v>1.294376978000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1845644922552699</v>
+        <v>0.1952386839672138</v>
       </c>
       <c r="T88">
-        <v>2.704778236268822</v>
+        <v>2.912838100597193</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1715361548035543</v>
+        <v>0.1695644748632836</v>
       </c>
       <c r="W88">
-        <v>0.1216184924748382</v>
+        <v>0.12190793509007</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9028218673871281</v>
+        <v>0.8924446045435979</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1314409324440987</v>
+        <v>0.1324509324440987</v>
       </c>
       <c r="C89">
-        <v>-43.81152427707302</v>
+        <v>-45.25615298476571</v>
       </c>
       <c r="D89">
-        <v>31.48497572292697</v>
+        <v>31.15984701523428</v>
       </c>
       <c r="E89">
-        <v>96.54649999999999</v>
+        <v>97.666</v>
       </c>
       <c r="F89">
-        <v>97.39649999999999</v>
+        <v>98.51599999999999</v>
       </c>
       <c r="G89">
         <v>22.1</v>
@@ -8585,37 +8585,37 @@
         <v>12.76</v>
       </c>
       <c r="M89">
-        <v>14.2978062</v>
+        <v>14.4621488</v>
       </c>
       <c r="N89">
-        <v>-1.537806199999999</v>
+        <v>-1.702148799999998</v>
       </c>
       <c r="O89">
-        <v>-0.2921831779999997</v>
+        <v>-0.3234082719999996</v>
       </c>
       <c r="P89">
-        <v>-1.245623021999999</v>
+        <v>-1.378740527999998</v>
       </c>
       <c r="Q89">
-        <v>1.294376978000001</v>
+        <v>1.161259472000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1952386839672138</v>
+        <v>0.2076919076311483</v>
       </c>
       <c r="T89">
-        <v>2.912838100597193</v>
+        <v>3.155574608980293</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1695644748632836</v>
+        <v>0.1676376058307463</v>
       </c>
       <c r="W89">
-        <v>0.12190793509007</v>
+        <v>0.1221907994640465</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8924446045435979</v>
+        <v>0.8823031885828752</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1324509324440987</v>
+        <v>0.1334609324440987</v>
       </c>
       <c r="C90">
-        <v>-45.25615298476571</v>
+        <v>-46.69413545985664</v>
       </c>
       <c r="D90">
-        <v>31.15984701523428</v>
+        <v>30.84136454014335</v>
       </c>
       <c r="E90">
-        <v>97.666</v>
+        <v>98.7855</v>
       </c>
       <c r="F90">
-        <v>98.51599999999999</v>
+        <v>99.63549999999999</v>
       </c>
       <c r="G90">
         <v>22.1</v>
@@ -8667,37 +8667,37 @@
         <v>12.76</v>
       </c>
       <c r="M90">
-        <v>14.4621488</v>
+        <v>14.6264914</v>
       </c>
       <c r="N90">
-        <v>-1.702148799999998</v>
+        <v>-1.866491399999999</v>
       </c>
       <c r="O90">
-        <v>-0.3234082719999996</v>
+        <v>-0.3546333659999998</v>
       </c>
       <c r="P90">
-        <v>-1.378740527999998</v>
+        <v>-1.511858033999999</v>
       </c>
       <c r="Q90">
-        <v>1.161259472000002</v>
+        <v>1.028141966000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2076919076311483</v>
+        <v>0.2224093537794345</v>
       </c>
       <c r="T90">
-        <v>3.155574608980293</v>
+        <v>3.442445027978501</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1676376058307463</v>
+        <v>0.1657540372259064</v>
       </c>
       <c r="W90">
-        <v>0.1221907994640465</v>
+        <v>0.1224673073352369</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8823031885828752</v>
+        <v>0.8723896696100338</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1334609324440987</v>
+        <v>0.1344709324440987</v>
       </c>
       <c r="C91">
-        <v>-46.69413545985664</v>
+        <v>-48.12567343242267</v>
       </c>
       <c r="D91">
-        <v>30.84136454014335</v>
+        <v>30.52932656757732</v>
       </c>
       <c r="E91">
-        <v>98.7855</v>
+        <v>99.905</v>
       </c>
       <c r="F91">
-        <v>99.63549999999999</v>
+        <v>100.755</v>
       </c>
       <c r="G91">
         <v>22.1</v>
@@ -8749,37 +8749,37 @@
         <v>12.76</v>
       </c>
       <c r="M91">
-        <v>14.6264914</v>
+        <v>14.790834</v>
       </c>
       <c r="N91">
-        <v>-1.866491399999999</v>
+        <v>-2.030833999999999</v>
       </c>
       <c r="O91">
-        <v>-0.3546333659999998</v>
+        <v>-0.3858584599999997</v>
       </c>
       <c r="P91">
-        <v>-1.511858033999999</v>
+        <v>-1.644975539999999</v>
       </c>
       <c r="Q91">
-        <v>1.028141966000001</v>
+        <v>0.895024460000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2224093537794345</v>
+        <v>0.240070289157378</v>
       </c>
       <c r="T91">
-        <v>3.442445027978501</v>
+        <v>3.786689530776352</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1657540372259064</v>
+        <v>0.1639123257011741</v>
       </c>
       <c r="W91">
-        <v>0.1224673073352369</v>
+        <v>0.1227376705870677</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8723896696100338</v>
+        <v>0.8626964510588112</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1344709324440987</v>
+        <v>0.1354809324440987</v>
       </c>
       <c r="C92">
-        <v>-48.12567343242267</v>
+        <v>-49.55096055028456</v>
       </c>
       <c r="D92">
-        <v>30.52932656757732</v>
+        <v>30.22353944971543</v>
       </c>
       <c r="E92">
-        <v>99.905</v>
+        <v>101.0245</v>
       </c>
       <c r="F92">
-        <v>100.755</v>
+        <v>101.8745</v>
       </c>
       <c r="G92">
         <v>22.1</v>
@@ -8831,37 +8831,37 @@
         <v>12.76</v>
       </c>
       <c r="M92">
-        <v>14.790834</v>
+        <v>14.9551766</v>
       </c>
       <c r="N92">
-        <v>-2.030833999999999</v>
+        <v>-2.1951766</v>
       </c>
       <c r="O92">
-        <v>-0.3858584599999997</v>
+        <v>-0.417083554</v>
       </c>
       <c r="P92">
-        <v>-1.644975539999999</v>
+        <v>-1.778093046</v>
       </c>
       <c r="Q92">
-        <v>0.895024460000001</v>
+        <v>0.7619069540000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.240070289157378</v>
+        <v>0.261655876841531</v>
       </c>
       <c r="T92">
-        <v>3.786689530776352</v>
+        <v>4.207432811973725</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1639123257011741</v>
+        <v>0.1621110913528096</v>
       </c>
       <c r="W92">
-        <v>0.1227376705870677</v>
+        <v>0.1230020917894076</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8626964510588112</v>
+        <v>0.8532162702779451</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1354809324440987</v>
+        <v>0.1364909324440987</v>
       </c>
       <c r="C93">
-        <v>-49.55096055028456</v>
+        <v>-50.97018277975953</v>
       </c>
       <c r="D93">
-        <v>30.22353944971543</v>
+        <v>29.92381722024047</v>
       </c>
       <c r="E93">
-        <v>101.0245</v>
+        <v>102.144</v>
       </c>
       <c r="F93">
-        <v>101.8745</v>
+        <v>102.994</v>
       </c>
       <c r="G93">
         <v>22.1</v>
@@ -8913,37 +8913,37 @@
         <v>12.76</v>
       </c>
       <c r="M93">
-        <v>14.9551766</v>
+        <v>15.1195192</v>
       </c>
       <c r="N93">
-        <v>-2.1951766</v>
+        <v>-2.359519199999999</v>
       </c>
       <c r="O93">
-        <v>-0.417083554</v>
+        <v>-0.4483086479999999</v>
       </c>
       <c r="P93">
-        <v>-1.778093046</v>
+        <v>-1.911210552</v>
       </c>
       <c r="Q93">
-        <v>0.7619069540000001</v>
+        <v>0.6287894480000005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.261655876841531</v>
+        <v>0.2886378614467225</v>
       </c>
       <c r="T93">
-        <v>4.207432811973725</v>
+        <v>4.733361913470442</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1621110913528096</v>
+        <v>0.1603490142728878</v>
       </c>
       <c r="W93">
-        <v>0.1230020917894076</v>
+        <v>0.1232607647047401</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8532162702779451</v>
+        <v>0.8439421803836197</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1364909324440987</v>
+        <v>0.1375009324440987</v>
       </c>
       <c r="C94">
-        <v>-50.97018277975953</v>
+        <v>-52.38351878280262</v>
       </c>
       <c r="D94">
-        <v>29.92381722024047</v>
+        <v>29.62998121719737</v>
       </c>
       <c r="E94">
-        <v>102.144</v>
+        <v>103.2635</v>
       </c>
       <c r="F94">
-        <v>102.994</v>
+        <v>104.1135</v>
       </c>
       <c r="G94">
         <v>22.1</v>
@@ -8995,37 +8995,37 @@
         <v>12.76</v>
       </c>
       <c r="M94">
-        <v>15.1195192</v>
+        <v>15.2838618</v>
       </c>
       <c r="N94">
-        <v>-2.359519199999999</v>
+        <v>-2.523861800000001</v>
       </c>
       <c r="O94">
-        <v>-0.4483086479999999</v>
+        <v>-0.4795337420000001</v>
       </c>
       <c r="P94">
-        <v>-1.911210552</v>
+        <v>-2.044328058000001</v>
       </c>
       <c r="Q94">
-        <v>0.6287894480000005</v>
+        <v>0.4956719419999995</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2886378614467225</v>
+        <v>0.32332898451054</v>
       </c>
       <c r="T94">
-        <v>4.733361913470442</v>
+        <v>5.409556472537648</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1603490142728878</v>
+        <v>0.1586248313237169</v>
       </c>
       <c r="W94">
-        <v>0.1232607647047401</v>
+        <v>0.1235138747616784</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8439421803836197</v>
+        <v>0.8348675332827205</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1375009324440987</v>
+        <v>0.1385109324440987</v>
       </c>
       <c r="C95">
-        <v>-52.38351878280262</v>
+        <v>-53.79114027214431</v>
       </c>
       <c r="D95">
-        <v>29.62998121719737</v>
+        <v>29.34185972785568</v>
       </c>
       <c r="E95">
-        <v>103.2635</v>
+        <v>104.383</v>
       </c>
       <c r="F95">
-        <v>104.1135</v>
+        <v>105.233</v>
       </c>
       <c r="G95">
         <v>22.1</v>
@@ -9077,37 +9077,37 @@
         <v>12.76</v>
       </c>
       <c r="M95">
-        <v>15.2838618</v>
+        <v>15.4482044</v>
       </c>
       <c r="N95">
-        <v>-2.523861800000001</v>
+        <v>-2.688204399999998</v>
       </c>
       <c r="O95">
-        <v>-0.4795337420000001</v>
+        <v>-0.5107588359999997</v>
       </c>
       <c r="P95">
-        <v>-2.044328058000001</v>
+        <v>-2.177445563999998</v>
       </c>
       <c r="Q95">
-        <v>0.4956719419999995</v>
+        <v>0.3625544360000017</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.32332898451054</v>
+        <v>0.3695838152622968</v>
       </c>
       <c r="T95">
-        <v>5.409556472537648</v>
+        <v>6.311149217960592</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1586248313237169</v>
+        <v>0.1569373331181455</v>
       </c>
       <c r="W95">
-        <v>0.1235138747616784</v>
+        <v>0.1237615994982563</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8348675332827205</v>
+        <v>0.8259859637797129</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1385109324440987</v>
+        <v>0.1395209324440987</v>
       </c>
       <c r="C96">
-        <v>-53.79114027214431</v>
+        <v>-55.19321234590744</v>
       </c>
       <c r="D96">
-        <v>29.34185972785568</v>
+        <v>29.05928765409255</v>
       </c>
       <c r="E96">
-        <v>104.383</v>
+        <v>105.5025</v>
       </c>
       <c r="F96">
-        <v>105.233</v>
+        <v>106.3525</v>
       </c>
       <c r="G96">
         <v>22.1</v>
@@ -9159,37 +9159,37 @@
         <v>12.76</v>
       </c>
       <c r="M96">
-        <v>15.4482044</v>
+        <v>15.612547</v>
       </c>
       <c r="N96">
-        <v>-2.688204399999998</v>
+        <v>-2.852546999999999</v>
       </c>
       <c r="O96">
-        <v>-0.5107588359999997</v>
+        <v>-0.5419839299999999</v>
       </c>
       <c r="P96">
-        <v>-2.177445563999998</v>
+        <v>-2.31056307</v>
       </c>
       <c r="Q96">
-        <v>0.3625544360000017</v>
+        <v>0.2294369300000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3695838152622968</v>
+        <v>0.4343405783147564</v>
       </c>
       <c r="T96">
-        <v>6.311149217960592</v>
+        <v>7.573379061552713</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1569373331181455</v>
+        <v>0.155285361190586</v>
       </c>
       <c r="W96">
-        <v>0.1237615994982563</v>
+        <v>0.124004108977222</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8259859637797129</v>
+        <v>0.8172913746872948</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1395209324440987</v>
+        <v>0.1405309324440987</v>
       </c>
       <c r="C97">
-        <v>-55.19321234590744</v>
+        <v>-56.58989380307372</v>
       </c>
       <c r="D97">
-        <v>29.05928765409255</v>
+        <v>28.78210619692627</v>
       </c>
       <c r="E97">
-        <v>105.5025</v>
+        <v>106.622</v>
       </c>
       <c r="F97">
-        <v>106.3525</v>
+        <v>107.472</v>
       </c>
       <c r="G97">
         <v>22.1</v>
@@ -9241,37 +9241,37 @@
         <v>12.76</v>
       </c>
       <c r="M97">
-        <v>15.612547</v>
+        <v>15.7768896</v>
       </c>
       <c r="N97">
-        <v>-2.852546999999999</v>
+        <v>-3.016889599999999</v>
       </c>
       <c r="O97">
-        <v>-0.5419839299999999</v>
+        <v>-0.5732090239999998</v>
       </c>
       <c r="P97">
-        <v>-2.31056307</v>
+        <v>-2.443680575999999</v>
       </c>
       <c r="Q97">
-        <v>0.2294369300000003</v>
+        <v>0.09631942400000071</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4343405783147564</v>
+        <v>0.5314757228934456</v>
       </c>
       <c r="T97">
-        <v>7.573379061552713</v>
+        <v>9.466723826940894</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.155285361190586</v>
+        <v>0.1536678053448507</v>
       </c>
       <c r="W97">
-        <v>0.124004108977222</v>
+        <v>0.1242415661753759</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8172913746872948</v>
+        <v>0.8087779228676355</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1405309324440987</v>
+        <v>0.1415409324440987</v>
       </c>
       <c r="C98">
-        <v>-56.58989380307371</v>
+        <v>-57.98133744106649</v>
       </c>
       <c r="D98">
-        <v>28.78210619692627</v>
+        <v>28.51016255893349</v>
       </c>
       <c r="E98">
-        <v>106.622</v>
+        <v>107.7415</v>
       </c>
       <c r="F98">
-        <v>107.472</v>
+        <v>108.5915</v>
       </c>
       <c r="G98">
         <v>22.1</v>
@@ -9323,37 +9323,37 @@
         <v>12.76</v>
       </c>
       <c r="M98">
-        <v>15.7768896</v>
+        <v>15.9412322</v>
       </c>
       <c r="N98">
-        <v>-3.016889599999997</v>
+        <v>-3.181232199999997</v>
       </c>
       <c r="O98">
-        <v>-0.5732090239999995</v>
+        <v>-0.6044341179999994</v>
       </c>
       <c r="P98">
-        <v>-2.443680575999998</v>
+        <v>-2.576798081999997</v>
       </c>
       <c r="Q98">
-        <v>0.09631942400000248</v>
+        <v>-0.03679808199999712</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5314757228934442</v>
+        <v>0.6933676305245924</v>
       </c>
       <c r="T98">
-        <v>9.46672382694087</v>
+        <v>12.62229843592116</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1536678053448508</v>
+        <v>0.1520836011660379</v>
       </c>
       <c r="W98">
-        <v>0.1242415661753759</v>
+        <v>0.1244741273488256</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8087779228676356</v>
+        <v>0.8004400061370415</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1415409324440987</v>
+        <v>0.1963750125605633</v>
       </c>
       <c r="C99">
-        <v>-57.98133744106649</v>
+        <v>-68.76706651408918</v>
       </c>
       <c r="D99">
-        <v>28.51016255893349</v>
+        <v>18.8439334859108</v>
       </c>
       <c r="E99">
-        <v>107.7415</v>
+        <v>108.861</v>
       </c>
       <c r="F99">
-        <v>108.5915</v>
+        <v>109.711</v>
       </c>
       <c r="G99">
         <v>22.1</v>
@@ -9405,45 +9405,45 @@
         <v>12.76</v>
       </c>
       <c r="M99">
-        <v>15.9412322</v>
+        <v>22.0299688</v>
       </c>
       <c r="N99">
-        <v>-3.181232199999997</v>
+        <v>-9.269968799999997</v>
       </c>
       <c r="O99">
-        <v>-0.6044341179999994</v>
+        <v>-1.761294071999999</v>
       </c>
       <c r="P99">
-        <v>-2.576798081999997</v>
+        <v>-7.508674727999998</v>
       </c>
       <c r="Q99">
-        <v>-0.03679808199999712</v>
+        <v>-4.968674727999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6933676305245924</v>
+        <v>1.06235545161012</v>
       </c>
       <c r="T99">
-        <v>12.62229843592116</v>
+        <v>19.81455786554832</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1520836011660379</v>
+        <v>0.1100500877695297</v>
       </c>
       <c r="W99">
-        <v>0.1244741273488256</v>
+        <v>0.1787019423758785</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8004400061370415</v>
+        <v>0.5792109882606825</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1963750125605633</v>
+        <v>0.1979250125605633</v>
       </c>
       <c r="C100">
-        <v>-68.76706651408918</v>
+        <v>-70.06544895293494</v>
       </c>
       <c r="D100">
-        <v>18.8439334859108</v>
+        <v>18.66505104706504</v>
       </c>
       <c r="E100">
-        <v>108.861</v>
+        <v>109.9805</v>
       </c>
       <c r="F100">
-        <v>109.711</v>
+        <v>110.8305</v>
       </c>
       <c r="G100">
         <v>22.1</v>
@@ -9487,37 +9487,37 @@
         <v>12.76</v>
       </c>
       <c r="M100">
-        <v>22.0299688</v>
+        <v>22.2547644</v>
       </c>
       <c r="N100">
-        <v>-9.269968799999997</v>
+        <v>-9.494764399999998</v>
       </c>
       <c r="O100">
-        <v>-1.761294071999999</v>
+        <v>-1.804005236</v>
       </c>
       <c r="P100">
-        <v>-7.508674727999998</v>
+        <v>-7.690759163999997</v>
       </c>
       <c r="Q100">
-        <v>-4.968674727999998</v>
+        <v>-5.150759163999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.06235545161012</v>
+        <v>2.07891090322024</v>
       </c>
       <c r="T100">
-        <v>19.81455786554832</v>
+        <v>39.62911573109663</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1100500877695297</v>
+        <v>0.1089384707213526</v>
       </c>
       <c r="W100">
-        <v>0.1787019423758785</v>
+        <v>0.1789251550791524</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5792109882606825</v>
+        <v>0.5733603722176452</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1979250125605633</v>
-      </c>
-      <c r="C101">
-        <v>-70.06544895293494</v>
-      </c>
-      <c r="D101">
-        <v>18.66505104706504</v>
-      </c>
-      <c r="E101">
-        <v>109.9805</v>
-      </c>
-      <c r="F101">
-        <v>110.8305</v>
-      </c>
-      <c r="G101">
-        <v>22.1</v>
-      </c>
-      <c r="H101">
-        <v>111.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15.3</v>
-      </c>
-      <c r="K101">
-        <v>2.54</v>
-      </c>
-      <c r="L101">
-        <v>12.76</v>
-      </c>
-      <c r="M101">
-        <v>22.2547644</v>
-      </c>
-      <c r="N101">
-        <v>-9.494764399999998</v>
-      </c>
-      <c r="O101">
-        <v>-1.804005236</v>
-      </c>
-      <c r="P101">
-        <v>-7.690759163999997</v>
-      </c>
-      <c r="Q101">
-        <v>-5.150759163999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.07891090322024</v>
-      </c>
-      <c r="T101">
-        <v>39.62911573109663</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1089384707213526</v>
-      </c>
-      <c r="W101">
-        <v>0.1789251550791524</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5733603722176452</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
